--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828603</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532284</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160597</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828581</v>
+        <v>125828565</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532244</v>
+        <v>532478</v>
       </c>
       <c r="R3" t="n">
-        <v>7160561</v>
+        <v>7160743</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828585</v>
+        <v>125828564</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532547</v>
+        <v>532304</v>
       </c>
       <c r="R4" t="n">
-        <v>7160658</v>
+        <v>7160798</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828603</v>
+        <v>125828582</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532284</v>
+        <v>532233</v>
       </c>
       <c r="R5" t="n">
-        <v>7160597</v>
+        <v>7160402</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1126,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1112,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828565</v>
+        <v>125828581</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532478</v>
+        <v>532244</v>
       </c>
       <c r="R6" t="n">
-        <v>7160743</v>
+        <v>7160561</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,6 +1239,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828564</v>
+        <v>125828585</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,39 +1281,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532304</v>
+        <v>532547</v>
       </c>
       <c r="R7" t="n">
-        <v>7160798</v>
+        <v>7160658</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,6 +1366,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828566</v>
+        <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532509</v>
+        <v>532334</v>
       </c>
       <c r="R8" t="n">
-        <v>7160725</v>
+        <v>7160647</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828601</v>
+        <v>125828599</v>
       </c>
       <c r="B9" t="n">
         <v>78967</v>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532334</v>
+        <v>532603</v>
       </c>
       <c r="R9" t="n">
-        <v>7160647</v>
+        <v>7160632</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828599</v>
+        <v>125828604</v>
       </c>
       <c r="B10" t="n">
         <v>78967</v>
@@ -1656,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532603</v>
+        <v>532249</v>
       </c>
       <c r="R10" t="n">
-        <v>7160632</v>
+        <v>7160567</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1691,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828604</v>
+        <v>125828566</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532249</v>
+        <v>532509</v>
       </c>
       <c r="R11" t="n">
-        <v>7160567</v>
+        <v>7160725</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80030</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3097,32 +3097,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125828592</v>
+        <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>80106</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532509</v>
+        <v>532338</v>
       </c>
       <c r="R22" t="n">
-        <v>7160662</v>
+        <v>7160650</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3228,32 +3228,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125828595</v>
+        <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80106</v>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532338</v>
+        <v>532509</v>
       </c>
       <c r="R23" t="n">
-        <v>7160650</v>
+        <v>7160662</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828603</v>
+        <v>125828565</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532284</v>
+        <v>532478</v>
       </c>
       <c r="R2" t="n">
-        <v>7160597</v>
+        <v>7160743</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828565</v>
+        <v>125828564</v>
       </c>
       <c r="B3" t="n">
         <v>57651</v>
@@ -822,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532478</v>
+        <v>532304</v>
       </c>
       <c r="R3" t="n">
-        <v>7160743</v>
+        <v>7160798</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828564</v>
+        <v>125828582</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532304</v>
+        <v>532233</v>
       </c>
       <c r="R4" t="n">
-        <v>7160798</v>
+        <v>7160402</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1005,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828582</v>
+        <v>125828581</v>
       </c>
       <c r="B5" t="n">
         <v>80071</v>
@@ -1051,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532233</v>
+        <v>532244</v>
       </c>
       <c r="R5" t="n">
-        <v>7160402</v>
+        <v>7160561</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828581</v>
+        <v>125828585</v>
       </c>
       <c r="B6" t="n">
         <v>80071</v>
@@ -1178,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532244</v>
+        <v>532547</v>
       </c>
       <c r="R6" t="n">
-        <v>7160561</v>
+        <v>7160658</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828585</v>
+        <v>125828603</v>
       </c>
       <c r="B7" t="n">
-        <v>80071</v>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532547</v>
+        <v>532284</v>
       </c>
       <c r="R7" t="n">
-        <v>7160658</v>
+        <v>7160597</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1340,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,21 +1381,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828601</v>
+        <v>125828566</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532334</v>
+        <v>532509</v>
       </c>
       <c r="R8" t="n">
-        <v>7160647</v>
+        <v>7160725</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828599</v>
+        <v>125828601</v>
       </c>
       <c r="B9" t="n">
         <v>78967</v>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532603</v>
+        <v>532334</v>
       </c>
       <c r="R9" t="n">
-        <v>7160632</v>
+        <v>7160647</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828604</v>
+        <v>125828599</v>
       </c>
       <c r="B10" t="n">
         <v>78967</v>
@@ -1646,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532249</v>
+        <v>532603</v>
       </c>
       <c r="R10" t="n">
-        <v>7160567</v>
+        <v>7160632</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1681,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828566</v>
+        <v>125828604</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532509</v>
+        <v>532249</v>
       </c>
       <c r="R11" t="n">
-        <v>7160725</v>
+        <v>7160567</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2220,7 +2220,7 @@
         <v>125828598</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R18" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2692,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,32 +2726,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80030</v>
+        <v>80071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R19" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2806,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,23 +2820,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,34 +2864,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R20" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2933,12 +2938,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,21 +2954,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2980,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2991,39 +2981,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R21" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3055,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,12 +3050,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,6 +3066,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,37 +4219,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R31" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4281,7 +4278,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4291,12 +4288,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4305,23 +4302,22 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4339,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80106</v>
+        <v>80105</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4350,34 +4346,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R32" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,12 +4418,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4433,22 +4432,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828566</v>
+        <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532509</v>
+        <v>532334</v>
       </c>
       <c r="R8" t="n">
-        <v>7160725</v>
+        <v>7160647</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828601</v>
+        <v>125828599</v>
       </c>
       <c r="B9" t="n">
         <v>78967</v>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532334</v>
+        <v>532603</v>
       </c>
       <c r="R9" t="n">
-        <v>7160647</v>
+        <v>7160632</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828599</v>
+        <v>125828604</v>
       </c>
       <c r="B10" t="n">
         <v>78967</v>
@@ -1656,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532603</v>
+        <v>532249</v>
       </c>
       <c r="R10" t="n">
-        <v>7160632</v>
+        <v>7160567</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1691,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828604</v>
+        <v>125828566</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532249</v>
+        <v>532509</v>
       </c>
       <c r="R11" t="n">
-        <v>7160567</v>
+        <v>7160725</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828565</v>
+        <v>125828582</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532478</v>
+        <v>532233</v>
       </c>
       <c r="R2" t="n">
-        <v>7160743</v>
+        <v>7160402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828564</v>
+        <v>125828581</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532304</v>
+        <v>532244</v>
       </c>
       <c r="R3" t="n">
-        <v>7160798</v>
+        <v>7160561</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +898,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828582</v>
+        <v>125828585</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532233</v>
+        <v>532547</v>
       </c>
       <c r="R4" t="n">
-        <v>7160402</v>
+        <v>7160658</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828581</v>
+        <v>125828565</v>
       </c>
       <c r="B5" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,34 +1067,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532244</v>
+        <v>532478</v>
       </c>
       <c r="R5" t="n">
-        <v>7160561</v>
+        <v>7160743</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,21 +1157,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828585</v>
+        <v>125828564</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532547</v>
+        <v>532304</v>
       </c>
       <c r="R6" t="n">
-        <v>7160658</v>
+        <v>7160798</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1233,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1274,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>125828603</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>125828599</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125828604</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>125828593</v>
       </c>
       <c r="B12" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>125828586</v>
       </c>
       <c r="B13" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>125828588</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>125828598</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>91246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         <v>125828575</v>
       </c>
       <c r="B16" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>125828573</v>
       </c>
       <c r="B17" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,39 +2864,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R20" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2928,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,12 +2933,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,6 +2949,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2970,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,34 +2991,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R21" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3040,7 +3055,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,12 +3065,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,21 +3081,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3100,7 +3100,7 @@
         <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>125828584</v>
       </c>
       <c r="B26" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>125828572</v>
       </c>
       <c r="B29" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>125828600</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>125828583</v>
       </c>
       <c r="B33" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>125828576</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125828587</v>
       </c>
       <c r="B35" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828574</v>
+        <v>125828591</v>
       </c>
       <c r="B25" t="n">
-        <v>80072</v>
+        <v>80071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532502</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7160701</v>
+        <v>7160785</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828584</v>
+        <v>125828574</v>
       </c>
       <c r="B26" t="n">
         <v>80072</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532588</v>
+        <v>532502</v>
       </c>
       <c r="R26" t="n">
-        <v>7160699</v>
+        <v>7160701</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828591</v>
+        <v>125828584</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532441</v>
+        <v>532588</v>
       </c>
       <c r="R27" t="n">
-        <v>7160785</v>
+        <v>7160699</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828565</v>
       </c>
       <c r="B2" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532478</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160743</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828581</v>
+        <v>125828564</v>
       </c>
       <c r="B3" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532244</v>
+        <v>532304</v>
       </c>
       <c r="R3" t="n">
-        <v>7160561</v>
+        <v>7160798</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,21 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828585</v>
+        <v>125828582</v>
       </c>
       <c r="B4" t="n">
         <v>80072</v>
@@ -964,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532547</v>
+        <v>532233</v>
       </c>
       <c r="R4" t="n">
-        <v>7160658</v>
+        <v>7160402</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828565</v>
+        <v>125828581</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532478</v>
+        <v>532244</v>
       </c>
       <c r="R5" t="n">
-        <v>7160743</v>
+        <v>7160561</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1131,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828564</v>
+        <v>125828585</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>80072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532304</v>
+        <v>532547</v>
       </c>
       <c r="R6" t="n">
-        <v>7160798</v>
+        <v>7160658</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1248,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1259,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828601</v>
+        <v>125828566</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532334</v>
+        <v>532509</v>
       </c>
       <c r="R8" t="n">
-        <v>7160647</v>
+        <v>7160725</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828599</v>
+        <v>125828601</v>
       </c>
       <c r="B9" t="n">
         <v>78968</v>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532603</v>
+        <v>532334</v>
       </c>
       <c r="R9" t="n">
-        <v>7160632</v>
+        <v>7160647</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828604</v>
+        <v>125828599</v>
       </c>
       <c r="B10" t="n">
         <v>78968</v>
@@ -1646,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532249</v>
+        <v>532603</v>
       </c>
       <c r="R10" t="n">
-        <v>7160567</v>
+        <v>7160632</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1681,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828566</v>
+        <v>125828604</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532509</v>
+        <v>532249</v>
       </c>
       <c r="R11" t="n">
-        <v>7160725</v>
+        <v>7160567</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R25" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828574</v>
+        <v>125828584</v>
       </c>
       <c r="B26" t="n">
         <v>80072</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532502</v>
+        <v>532588</v>
       </c>
       <c r="R26" t="n">
-        <v>7160701</v>
+        <v>7160699</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80072</v>
+        <v>80071</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R27" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828565</v>
+        <v>125828582</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532478</v>
+        <v>532233</v>
       </c>
       <c r="R2" t="n">
-        <v>7160743</v>
+        <v>7160402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828564</v>
+        <v>125828581</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532304</v>
+        <v>532244</v>
       </c>
       <c r="R3" t="n">
-        <v>7160798</v>
+        <v>7160561</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +898,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828582</v>
+        <v>125828585</v>
       </c>
       <c r="B4" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532233</v>
+        <v>532547</v>
       </c>
       <c r="R4" t="n">
-        <v>7160402</v>
+        <v>7160658</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828581</v>
+        <v>125828603</v>
       </c>
       <c r="B5" t="n">
-        <v>80072</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532244</v>
+        <v>532284</v>
       </c>
       <c r="R5" t="n">
-        <v>7160561</v>
+        <v>7160597</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828585</v>
+        <v>125828565</v>
       </c>
       <c r="B6" t="n">
-        <v>80072</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1174,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532547</v>
+        <v>532478</v>
       </c>
       <c r="R6" t="n">
-        <v>7160658</v>
+        <v>7160743</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1264,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828603</v>
+        <v>125828564</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1291,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532284</v>
+        <v>532304</v>
       </c>
       <c r="R7" t="n">
-        <v>7160597</v>
+        <v>7160798</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1360,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828566</v>
+        <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532509</v>
+        <v>532334</v>
       </c>
       <c r="R8" t="n">
-        <v>7160725</v>
+        <v>7160647</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828601</v>
+        <v>125828599</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532334</v>
+        <v>532603</v>
       </c>
       <c r="R9" t="n">
-        <v>7160647</v>
+        <v>7160632</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828599</v>
+        <v>125828604</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532603</v>
+        <v>532249</v>
       </c>
       <c r="R10" t="n">
-        <v>7160632</v>
+        <v>7160567</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1691,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828604</v>
+        <v>125828566</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532249</v>
+        <v>532509</v>
       </c>
       <c r="R11" t="n">
-        <v>7160567</v>
+        <v>7160725</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>125828593</v>
       </c>
       <c r="B12" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>125828586</v>
       </c>
       <c r="B13" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>91250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R14" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B15" t="n">
-        <v>91246</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R15" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
         <v>125828575</v>
       </c>
       <c r="B16" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>125828573</v>
       </c>
       <c r="B17" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80031</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80072</v>
+        <v>80035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>125828584</v>
       </c>
       <c r="B26" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>125828572</v>
       </c>
       <c r="B29" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>125828600</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80107</v>
+        <v>80111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>125828583</v>
       </c>
       <c r="B33" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>125828576</v>
       </c>
       <c r="B34" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125828587</v>
       </c>
       <c r="B35" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B14" t="n">
-        <v>91250</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R14" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>91250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R15" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -1056,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828603</v>
+        <v>125828565</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,34 +1067,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532284</v>
+        <v>532478</v>
       </c>
       <c r="R5" t="n">
-        <v>7160597</v>
+        <v>7160743</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1126,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828565</v>
+        <v>125828564</v>
       </c>
       <c r="B6" t="n">
         <v>57651</v>
@@ -1203,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532478</v>
+        <v>532304</v>
       </c>
       <c r="R6" t="n">
-        <v>7160743</v>
+        <v>7160798</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828564</v>
+        <v>125828603</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,39 +1301,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532304</v>
+        <v>532284</v>
       </c>
       <c r="R7" t="n">
-        <v>7160798</v>
+        <v>7160597</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska och gamla ringhack</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,34 +2864,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R20" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2933,12 +2938,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,21 +2954,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2980,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2991,39 +2981,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R21" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3055,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,12 +3050,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,6 +3066,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828574</v>
+        <v>125828591</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532502</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7160701</v>
+        <v>7160785</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828584</v>
+        <v>125828574</v>
       </c>
       <c r="B26" t="n">
         <v>80076</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532588</v>
+        <v>532502</v>
       </c>
       <c r="R26" t="n">
-        <v>7160699</v>
+        <v>7160701</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828591</v>
+        <v>125828584</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532441</v>
+        <v>532588</v>
       </c>
       <c r="R27" t="n">
-        <v>7160785</v>
+        <v>7160699</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B31" t="n">
-        <v>80111</v>
+        <v>80110</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,34 +4219,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R31" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4278,7 +4281,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4288,12 +4291,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4302,22 +4305,23 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4335,10 +4339,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B32" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4346,37 +4350,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R32" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4418,12 +4419,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4432,23 +4433,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>80035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R18" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2692,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,32 +2726,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80035</v>
+        <v>80076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R19" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2806,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,23 +2820,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R25" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828574</v>
+        <v>125828584</v>
       </c>
       <c r="B26" t="n">
         <v>80076</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532502</v>
+        <v>532588</v>
       </c>
       <c r="R26" t="n">
-        <v>7160701</v>
+        <v>7160699</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R27" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>80075</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,39 +2864,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R20" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2928,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,12 +2933,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,6 +2949,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2970,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>57651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,34 +2991,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R21" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3040,7 +3055,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,12 +3065,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,21 +3081,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828574</v>
+        <v>125828591</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532502</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7160701</v>
+        <v>7160785</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828584</v>
+        <v>125828574</v>
       </c>
       <c r="B26" t="n">
         <v>80076</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532588</v>
+        <v>532502</v>
       </c>
       <c r="R26" t="n">
-        <v>7160699</v>
+        <v>7160701</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828591</v>
+        <v>125828584</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532441</v>
+        <v>532588</v>
       </c>
       <c r="R27" t="n">
-        <v>7160785</v>
+        <v>7160699</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828565</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532478</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160743</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +776,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828581</v>
+        <v>125828564</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532244</v>
+        <v>532304</v>
       </c>
       <c r="R3" t="n">
-        <v>7160561</v>
+        <v>7160798</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,21 +893,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828585</v>
+        <v>125828582</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532547</v>
+        <v>532233</v>
       </c>
       <c r="R4" t="n">
-        <v>7160658</v>
+        <v>7160402</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828565</v>
+        <v>125828581</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532478</v>
+        <v>532244</v>
       </c>
       <c r="R5" t="n">
-        <v>7160743</v>
+        <v>7160561</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1131,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828564</v>
+        <v>125828585</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>80077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,39 +1174,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532304</v>
+        <v>532547</v>
       </c>
       <c r="R6" t="n">
-        <v>7160798</v>
+        <v>7160658</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1248,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,6 +1259,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1293,7 +1293,7 @@
         <v>125828603</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>125828599</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>125828604</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>125828566</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>125828593</v>
       </c>
       <c r="B12" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>125828586</v>
       </c>
       <c r="B13" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>91252</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R14" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B15" t="n">
-        <v>91250</v>
+        <v>80076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R15" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
         <v>125828575</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>125828573</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80035</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>125828563</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R25" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828574</v>
+        <v>125828584</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532502</v>
+        <v>532588</v>
       </c>
       <c r="R26" t="n">
-        <v>7160701</v>
+        <v>7160699</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,7 +3730,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B27" t="n">
         <v>80076</v>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R27" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,7 +3860,7 @@
         <v>125828567</v>
       </c>
       <c r="B28" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>125828572</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>125828600</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80110</v>
+        <v>80112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,37 +4219,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R31" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4281,7 +4278,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4291,12 +4288,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4305,23 +4302,22 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4339,7 +4335,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B32" t="n">
         <v>80111</v>
@@ -4350,34 +4346,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R32" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,12 +4418,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4433,22 +4432,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
         <v>125828583</v>
       </c>
       <c r="B33" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>125828576</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125828587</v>
       </c>
       <c r="B35" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828565</v>
+        <v>125828603</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532478</v>
+        <v>532284</v>
       </c>
       <c r="R2" t="n">
-        <v>7160743</v>
+        <v>7160597</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828564</v>
+        <v>125828582</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532304</v>
+        <v>532233</v>
       </c>
       <c r="R3" t="n">
-        <v>7160798</v>
+        <v>7160402</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,6 +878,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828582</v>
+        <v>125828581</v>
       </c>
       <c r="B4" t="n">
         <v>80077</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532233</v>
+        <v>532244</v>
       </c>
       <c r="R4" t="n">
-        <v>7160402</v>
+        <v>7160561</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1036,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828581</v>
+        <v>125828585</v>
       </c>
       <c r="B5" t="n">
         <v>80077</v>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532244</v>
+        <v>532547</v>
       </c>
       <c r="R5" t="n">
-        <v>7160561</v>
+        <v>7160658</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828585</v>
+        <v>125828565</v>
       </c>
       <c r="B6" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,34 +1174,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532547</v>
+        <v>532478</v>
       </c>
       <c r="R6" t="n">
-        <v>7160658</v>
+        <v>7160743</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1233,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,21 +1264,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1290,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828603</v>
+        <v>125828564</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1291,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532284</v>
+        <v>532304</v>
       </c>
       <c r="R7" t="n">
-        <v>7160597</v>
+        <v>7160798</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1360,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828603</v>
+        <v>125828582</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532284</v>
+        <v>532233</v>
       </c>
       <c r="R2" t="n">
-        <v>7160597</v>
+        <v>7160402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828582</v>
+        <v>125828581</v>
       </c>
       <c r="B3" t="n">
         <v>80077</v>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532233</v>
+        <v>532244</v>
       </c>
       <c r="R3" t="n">
-        <v>7160402</v>
+        <v>7160561</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828581</v>
+        <v>125828585</v>
       </c>
       <c r="B4" t="n">
         <v>80077</v>
@@ -944,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532244</v>
+        <v>532547</v>
       </c>
       <c r="R4" t="n">
-        <v>7160561</v>
+        <v>7160658</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -979,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828585</v>
+        <v>125828603</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532547</v>
+        <v>532284</v>
       </c>
       <c r="R5" t="n">
-        <v>7160658</v>
+        <v>7160597</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2093,7 +2093,7 @@
         <v>125828598</v>
       </c>
       <c r="B14" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R18" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2692,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,32 +2726,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80036</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R19" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2806,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,23 +2820,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,34 +4219,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R31" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4278,7 +4281,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4288,12 +4291,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4302,22 +4305,23 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4335,10 +4339,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B32" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4346,37 +4350,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R32" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4418,12 +4419,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4432,23 +4433,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80036</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>80036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,34 +2864,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R20" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2923,7 +2928,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2933,12 +2938,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2949,21 +2954,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2980,10 +2970,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2991,39 +2981,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R21" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3055,7 +3040,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3065,12 +3050,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,6 +3066,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828603</v>
       </c>
       <c r="B2" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532284</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160597</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828581</v>
+        <v>125828565</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532244</v>
+        <v>532478</v>
       </c>
       <c r="R3" t="n">
-        <v>7160561</v>
+        <v>7160743</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -929,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828585</v>
+        <v>125828564</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,34 +910,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532547</v>
+        <v>532304</v>
       </c>
       <c r="R4" t="n">
-        <v>7160658</v>
+        <v>7160798</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,21 +1000,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1056,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828603</v>
+        <v>125828582</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532284</v>
+        <v>532233</v>
       </c>
       <c r="R5" t="n">
-        <v>7160597</v>
+        <v>7160402</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1126,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1096,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1112,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1163,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828565</v>
+        <v>125828581</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532478</v>
+        <v>532244</v>
       </c>
       <c r="R6" t="n">
-        <v>7160743</v>
+        <v>7160561</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1238,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1248,12 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,6 +1239,21 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1280,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828564</v>
+        <v>125828585</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,39 +1281,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532304</v>
+        <v>532547</v>
       </c>
       <c r="R7" t="n">
-        <v>7160798</v>
+        <v>7160658</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1355,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,12 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,6 +1366,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828601</v>
+        <v>125828566</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532334</v>
+        <v>532509</v>
       </c>
       <c r="R8" t="n">
-        <v>7160647</v>
+        <v>7160725</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,7 +1514,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828599</v>
+        <v>125828601</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532603</v>
+        <v>532334</v>
       </c>
       <c r="R9" t="n">
-        <v>7160632</v>
+        <v>7160647</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1621,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828604</v>
+        <v>125828599</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1646,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532249</v>
+        <v>532603</v>
       </c>
       <c r="R10" t="n">
-        <v>7160567</v>
+        <v>7160632</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1681,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828566</v>
+        <v>125828604</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532509</v>
+        <v>532249</v>
       </c>
       <c r="R11" t="n">
-        <v>7160725</v>
+        <v>7160567</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B14" t="n">
-        <v>91254</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R14" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B15" t="n">
-        <v>80076</v>
+        <v>91256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R15" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2344,32 +2344,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125828575</v>
+        <v>125828573</v>
       </c>
       <c r="B16" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532554</v>
+        <v>532502</v>
       </c>
       <c r="R16" t="n">
-        <v>7160491</v>
+        <v>7160701</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2471,32 +2471,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125828573</v>
+        <v>125828575</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532502</v>
+        <v>532554</v>
       </c>
       <c r="R17" t="n">
-        <v>7160701</v>
+        <v>7160491</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R18" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2692,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,32 +2726,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80036</v>
+        <v>80077</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R19" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2806,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,23 +2820,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125828569</v>
+        <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2864,39 +2864,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>532492</v>
+        <v>532254</v>
       </c>
       <c r="R20" t="n">
-        <v>7160686</v>
+        <v>7160427</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2928,7 +2923,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2938,12 +2933,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Gamla ringhack</t>
+          <t>På fallen sälgstam med levande unga stammar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2954,6 +2949,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2970,10 +2980,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125828571</v>
+        <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2981,34 +2991,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>532254</v>
+        <v>532492</v>
       </c>
       <c r="R21" t="n">
-        <v>7160427</v>
+        <v>7160686</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3040,7 +3055,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3050,12 +3065,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På fallen sälgstam med levande unga stammar</t>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3066,21 +3081,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3097,32 +3097,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125828595</v>
+        <v>125828592</v>
       </c>
       <c r="B22" t="n">
-        <v>80112</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532338</v>
+        <v>532509</v>
       </c>
       <c r="R22" t="n">
-        <v>7160650</v>
+        <v>7160662</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3228,32 +3228,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125828592</v>
+        <v>125828595</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>80112</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532509</v>
+        <v>532338</v>
       </c>
       <c r="R23" t="n">
-        <v>7160662</v>
+        <v>7160650</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828574</v>
+        <v>125828591</v>
       </c>
       <c r="B25" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532502</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7160701</v>
+        <v>7160785</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828584</v>
+        <v>125828574</v>
       </c>
       <c r="B26" t="n">
         <v>80077</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532588</v>
+        <v>532502</v>
       </c>
       <c r="R26" t="n">
-        <v>7160699</v>
+        <v>7160701</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828591</v>
+        <v>125828584</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532441</v>
+        <v>532588</v>
       </c>
       <c r="R27" t="n">
-        <v>7160785</v>
+        <v>7160699</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80111</v>
+        <v>80112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,37 +4219,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R31" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4281,7 +4278,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4291,12 +4288,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4305,23 +4302,22 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4339,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80112</v>
+        <v>80111</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4350,34 +4346,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R32" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,12 +4418,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4433,22 +4432,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828603</v>
+        <v>125828582</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>80077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532284</v>
+        <v>532233</v>
       </c>
       <c r="R2" t="n">
-        <v>7160597</v>
+        <v>7160402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828565</v>
+        <v>125828581</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532478</v>
+        <v>532244</v>
       </c>
       <c r="R3" t="n">
-        <v>7160743</v>
+        <v>7160561</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -857,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,6 +898,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -899,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828564</v>
+        <v>125828585</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,39 +940,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532304</v>
+        <v>532547</v>
       </c>
       <c r="R4" t="n">
-        <v>7160798</v>
+        <v>7160658</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -974,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1025,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828582</v>
+        <v>125828565</v>
       </c>
       <c r="B5" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,34 +1067,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532233</v>
+        <v>532478</v>
       </c>
       <c r="R5" t="n">
-        <v>7160402</v>
+        <v>7160743</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1086,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1141,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,21 +1157,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828581</v>
+        <v>125828564</v>
       </c>
       <c r="B6" t="n">
-        <v>80077</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,34 +1184,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532244</v>
+        <v>532304</v>
       </c>
       <c r="R6" t="n">
-        <v>7160561</v>
+        <v>7160798</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1213,7 +1248,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1258,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,21 +1274,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828585</v>
+        <v>125828603</v>
       </c>
       <c r="B7" t="n">
-        <v>80077</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532547</v>
+        <v>532284</v>
       </c>
       <c r="R7" t="n">
-        <v>7160658</v>
+        <v>7160597</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1340,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,21 +1381,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828566</v>
+        <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532509</v>
+        <v>532334</v>
       </c>
       <c r="R8" t="n">
-        <v>7160725</v>
+        <v>7160647</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828601</v>
+        <v>125828599</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532334</v>
+        <v>532603</v>
       </c>
       <c r="R9" t="n">
-        <v>7160647</v>
+        <v>7160632</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828599</v>
+        <v>125828566</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,34 +1622,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532603</v>
+        <v>532509</v>
       </c>
       <c r="R10" t="n">
-        <v>7160632</v>
+        <v>7160725</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80036</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80077</v>
+        <v>80036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R25" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828574</v>
+        <v>125828584</v>
       </c>
       <c r="B26" t="n">
         <v>80077</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532502</v>
+        <v>532588</v>
       </c>
       <c r="R26" t="n">
-        <v>7160701</v>
+        <v>7160699</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R27" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828603</v>
       </c>
       <c r="B2" t="n">
-        <v>80077</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532284</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160597</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828581</v>
+        <v>125828582</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532244</v>
+        <v>532233</v>
       </c>
       <c r="R3" t="n">
-        <v>7160561</v>
+        <v>7160402</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -929,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125828585</v>
+        <v>125828581</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532547</v>
+        <v>532244</v>
       </c>
       <c r="R4" t="n">
-        <v>7160658</v>
+        <v>7160561</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828565</v>
+        <v>125828585</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>80081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532478</v>
+        <v>532547</v>
       </c>
       <c r="R5" t="n">
-        <v>7160743</v>
+        <v>7160658</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1131,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,12 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125828564</v>
+        <v>125828565</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,10 +1203,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532304</v>
+        <v>532478</v>
       </c>
       <c r="R6" t="n">
-        <v>7160798</v>
+        <v>7160743</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1248,7 +1238,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1258,12 +1248,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska och gamla ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1290,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125828603</v>
+        <v>125828564</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1291,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532284</v>
+        <v>532304</v>
       </c>
       <c r="R7" t="n">
-        <v>7160597</v>
+        <v>7160798</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1360,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1370,7 +1365,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska och gamla ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828601</v>
+        <v>125828566</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532334</v>
+        <v>532509</v>
       </c>
       <c r="R8" t="n">
-        <v>7160647</v>
+        <v>7160725</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828599</v>
+        <v>125828601</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532603</v>
+        <v>532334</v>
       </c>
       <c r="R9" t="n">
-        <v>7160632</v>
+        <v>7160647</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828566</v>
+        <v>125828599</v>
       </c>
       <c r="B10" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1622,39 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532509</v>
+        <v>532603</v>
       </c>
       <c r="R10" t="n">
-        <v>7160725</v>
+        <v>7160632</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
         <v>125828604</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>125828593</v>
       </c>
       <c r="B12" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>125828586</v>
       </c>
       <c r="B13" t="n">
-        <v>80112</v>
+        <v>80116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>91260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R14" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B15" t="n">
-        <v>91256</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R15" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2344,32 +2344,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125828573</v>
+        <v>125828575</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>532502</v>
+        <v>532554</v>
       </c>
       <c r="R16" t="n">
-        <v>7160701</v>
+        <v>7160491</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2471,32 +2471,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125828575</v>
+        <v>125828573</v>
       </c>
       <c r="B17" t="n">
-        <v>80112</v>
+        <v>80080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>532554</v>
+        <v>532502</v>
       </c>
       <c r="R17" t="n">
-        <v>7160491</v>
+        <v>7160701</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2601,7 +2601,7 @@
         <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3097,32 +3097,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125828592</v>
+        <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>80116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>532509</v>
+        <v>532338</v>
       </c>
       <c r="R22" t="n">
-        <v>7160662</v>
+        <v>7160650</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3228,32 +3228,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125828595</v>
+        <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80112</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>532338</v>
+        <v>532509</v>
       </c>
       <c r="R23" t="n">
-        <v>7160650</v>
+        <v>7160662</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3362,7 +3362,7 @@
         <v>125828563</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B26" t="n">
-        <v>80077</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,21 +3614,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R26" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828591</v>
+        <v>125828584</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532441</v>
+        <v>532588</v>
       </c>
       <c r="R27" t="n">
-        <v>7160785</v>
+        <v>7160699</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3860,7 +3860,7 @@
         <v>125828567</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>125828572</v>
       </c>
       <c r="B29" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>125828600</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>80115</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,34 +4219,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R31" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4278,7 +4281,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4288,12 +4291,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4302,22 +4305,23 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4335,10 +4339,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B32" t="n">
-        <v>80111</v>
+        <v>80116</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4346,37 +4350,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R32" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4408,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4418,12 +4419,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4432,23 +4433,22 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4469,7 +4469,7 @@
         <v>125828583</v>
       </c>
       <c r="B33" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>125828576</v>
       </c>
       <c r="B34" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125828587</v>
       </c>
       <c r="B35" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828566</v>
+        <v>125828601</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532509</v>
+        <v>532334</v>
       </c>
       <c r="R8" t="n">
-        <v>7160725</v>
+        <v>7160647</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1472,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1482,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828601</v>
+        <v>125828599</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1549,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532334</v>
+        <v>532603</v>
       </c>
       <c r="R9" t="n">
-        <v>7160647</v>
+        <v>7160632</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1584,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,7 +1611,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828599</v>
+        <v>125828604</v>
       </c>
       <c r="B10" t="n">
         <v>78977</v>
@@ -1656,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532603</v>
+        <v>532249</v>
       </c>
       <c r="R10" t="n">
-        <v>7160632</v>
+        <v>7160567</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1691,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1691,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828604</v>
+        <v>125828566</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,34 +1729,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532249</v>
+        <v>532509</v>
       </c>
       <c r="R11" t="n">
-        <v>7160567</v>
+        <v>7160725</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1798,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B18" t="n">
-        <v>80081</v>
+        <v>80040</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R18" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,22 +2692,23 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2725,32 +2726,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B19" t="n">
-        <v>80040</v>
+        <v>80081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2760,10 +2761,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R19" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2795,7 +2796,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2805,12 +2806,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,23 +2820,22 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828574</v>
+        <v>125828591</v>
       </c>
       <c r="B25" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532502</v>
+        <v>532441</v>
       </c>
       <c r="R25" t="n">
-        <v>7160701</v>
+        <v>7160785</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,10 +3603,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3614,21 +3614,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R26" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,12 +3683,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4208,10 +4208,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125828594</v>
+        <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80115</v>
+        <v>80116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4219,37 +4219,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>532338</v>
+        <v>532248</v>
       </c>
       <c r="R31" t="n">
-        <v>7160650</v>
+        <v>7160558</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -4281,7 +4278,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4291,12 +4288,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4305,23 +4302,22 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4339,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125828578</v>
+        <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80116</v>
+        <v>80115</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4350,34 +4346,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>532248</v>
+        <v>532338</v>
       </c>
       <c r="R32" t="n">
-        <v>7160558</v>
+        <v>7160650</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,12 +4418,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4433,22 +4432,23 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828603</v>
+        <v>125828582</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>80081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532284</v>
+        <v>532233</v>
       </c>
       <c r="R2" t="n">
-        <v>7160597</v>
+        <v>7160402</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828582</v>
+        <v>125828585</v>
       </c>
       <c r="B3" t="n">
         <v>80081</v>
@@ -817,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532233</v>
+        <v>532547</v>
       </c>
       <c r="R3" t="n">
-        <v>7160402</v>
+        <v>7160658</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -852,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1036,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828585</v>
+        <v>125828603</v>
       </c>
       <c r="B5" t="n">
-        <v>80081</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1067,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532547</v>
+        <v>532284</v>
       </c>
       <c r="R5" t="n">
-        <v>7160658</v>
+        <v>7160597</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,21 +1147,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B14" t="n">
-        <v>91260</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R14" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>91260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R15" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2598,32 +2598,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125828605</v>
+        <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80040</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>532391</v>
+        <v>532248</v>
       </c>
       <c r="R18" t="n">
-        <v>7160663</v>
+        <v>7160558</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På levande asp</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2692,23 +2692,22 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2726,32 +2725,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125828579</v>
+        <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80081</v>
+        <v>80040</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2761,10 +2760,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>532248</v>
+        <v>532391</v>
       </c>
       <c r="R19" t="n">
-        <v>7160558</v>
+        <v>7160663</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2796,7 +2795,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2806,12 +2805,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande asp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2820,22 +2819,23 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125828591</v>
+        <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3487,21 +3487,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3511,10 +3511,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>532441</v>
+        <v>532502</v>
       </c>
       <c r="R25" t="n">
-        <v>7160785</v>
+        <v>7160701</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,7 +3603,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125828574</v>
+        <v>125828584</v>
       </c>
       <c r="B26" t="n">
         <v>80081</v>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>532502</v>
+        <v>532588</v>
       </c>
       <c r="R26" t="n">
-        <v>7160701</v>
+        <v>7160699</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3730,10 +3730,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125828584</v>
+        <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3741,21 +3741,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3765,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>532588</v>
+        <v>532441</v>
       </c>
       <c r="R27" t="n">
-        <v>7160699</v>
+        <v>7160785</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125828582</v>
+        <v>125828603</v>
       </c>
       <c r="B2" t="n">
-        <v>80081</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532233</v>
+        <v>532284</v>
       </c>
       <c r="R2" t="n">
-        <v>7160402</v>
+        <v>7160597</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På levande sälg</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125828585</v>
+        <v>125828582</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532547</v>
+        <v>532233</v>
       </c>
       <c r="R3" t="n">
-        <v>7160658</v>
+        <v>7160402</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -872,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +912,7 @@
         <v>125828581</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125828603</v>
+        <v>125828585</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>80084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532284</v>
+        <v>532547</v>
       </c>
       <c r="R5" t="n">
-        <v>7160597</v>
+        <v>7160658</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1126,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,6 +1132,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1166,7 +1166,7 @@
         <v>125828565</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
         <v>125828564</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125828601</v>
+        <v>125828566</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>532334</v>
+        <v>532509</v>
       </c>
       <c r="R8" t="n">
-        <v>7160647</v>
+        <v>7160725</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gamla ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125828599</v>
+        <v>125828601</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1549,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>532603</v>
+        <v>532334</v>
       </c>
       <c r="R9" t="n">
-        <v>7160632</v>
+        <v>7160647</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1574,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125828604</v>
+        <v>125828599</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>532249</v>
+        <v>532603</v>
       </c>
       <c r="R10" t="n">
-        <v>7160567</v>
+        <v>7160632</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1681,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,10 +1728,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125828566</v>
+        <v>125828604</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,39 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gardamyrvägen, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>532509</v>
+        <v>532249</v>
       </c>
       <c r="R11" t="n">
-        <v>7160725</v>
+        <v>7160567</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gamla ringhack</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,7 +1838,7 @@
         <v>125828593</v>
       </c>
       <c r="B12" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>125828586</v>
       </c>
       <c r="B13" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125828588</v>
+        <v>125828598</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>91263</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,21 +2101,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>532568</v>
+        <v>532583</v>
       </c>
       <c r="R14" t="n">
-        <v>7160702</v>
+        <v>7160528</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På levande sälg</t>
+          <t>På levande gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,17 +2189,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125828598</v>
+        <v>125828588</v>
       </c>
       <c r="B15" t="n">
-        <v>91260</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,21 +2228,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>532583</v>
+        <v>532568</v>
       </c>
       <c r="R15" t="n">
-        <v>7160528</v>
+        <v>7160702</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På levande gran</t>
+          <t>På levande sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,17 +2316,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2347,7 +2347,7 @@
         <v>125828575</v>
       </c>
       <c r="B16" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>125828573</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>125828579</v>
       </c>
       <c r="B18" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>125828605</v>
       </c>
       <c r="B19" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>125828571</v>
       </c>
       <c r="B20" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>125828569</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         <v>125828595</v>
       </c>
       <c r="B22" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>125828592</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>125828563</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>125828574</v>
       </c>
       <c r="B25" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>125828584</v>
       </c>
       <c r="B26" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3733,7 +3733,7 @@
         <v>125828591</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>125828567</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>125828572</v>
       </c>
       <c r="B29" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>125828600</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>125828578</v>
       </c>
       <c r="B31" t="n">
-        <v>80116</v>
+        <v>80119</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>125828594</v>
       </c>
       <c r="B32" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>125828583</v>
       </c>
       <c r="B33" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>125828576</v>
       </c>
       <c r="B34" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>125828587</v>
       </c>
       <c r="B35" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4845,6 +4845,4859 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129995737</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>532200</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7160691</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129995736</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>532620</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7160691</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129995760</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>532511</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7160701</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129995772</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>532563</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7160749</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129995741</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>532146</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7160573</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129995752</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>532432</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7160788</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129995781</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>532429</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7160722</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129995776</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80189</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>532526</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7160704</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129995770</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>532587</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7160733</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129995739</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>532158</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7160507</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129995744</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>532040</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7160538</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129995763</v>
+      </c>
+      <c r="B47" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>532539</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7160707</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129995766</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>532620</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7160493</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129995780</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>532432</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7160802</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129995750</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>532257</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7160770</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129995748</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>532226</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7160724</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129995747</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>532181</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7160703</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129995767</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>532608</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7160642</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129995757</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>532504</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7160709</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129995755</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78841</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>532399</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7160737</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129995769</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>532626</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7160718</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129995759</v>
+      </c>
+      <c r="B57" t="n">
+        <v>80190</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>532498</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7160682</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129995745</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>532176</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7160588</v>
+      </c>
+      <c r="S58" t="n">
+        <v>2</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129995753</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>532432</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7160788</v>
+      </c>
+      <c r="S59" t="n">
+        <v>2</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129995762</v>
+      </c>
+      <c r="B60" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>532540</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7160698</v>
+      </c>
+      <c r="S60" t="n">
+        <v>3</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129995771</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>532562</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7160754</v>
+      </c>
+      <c r="S61" t="n">
+        <v>3</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129995756</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79703</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>532387</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7160719</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129995779</v>
+      </c>
+      <c r="B63" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>532445</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7160791</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129995774</v>
+      </c>
+      <c r="B64" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>532519</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7160765</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129995777</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>532500</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7160787</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129995775</v>
+      </c>
+      <c r="B66" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>532521</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7160766</v>
+      </c>
+      <c r="S66" t="n">
+        <v>3</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129995782</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79703</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>532409</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7160698</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129995773</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>532558</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7160752</v>
+      </c>
+      <c r="S68" t="n">
+        <v>2</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129995758</v>
+      </c>
+      <c r="B69" t="n">
+        <v>80189</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>532501</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7160693</v>
+      </c>
+      <c r="S69" t="n">
+        <v>2</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129995798</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98815</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>532493</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7160688</v>
+      </c>
+      <c r="S70" t="n">
+        <v>4</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129995768</v>
+      </c>
+      <c r="B71" t="n">
+        <v>80093</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>532602</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7160718</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129995751</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>532397</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7160829</v>
+      </c>
+      <c r="S72" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129995735</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91623</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>532609</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7160604</v>
+      </c>
+      <c r="S73" t="n">
+        <v>2</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129995738</v>
+      </c>
+      <c r="B74" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>532209</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7160509</v>
+      </c>
+      <c r="S74" t="n">
+        <v>2</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129995743</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>532052</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7160499</v>
+      </c>
+      <c r="S75" t="n">
+        <v>2</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129995740</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>532123</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7160541</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129995749</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>532259</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7160727</v>
+      </c>
+      <c r="S77" t="n">
+        <v>2</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129995778</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80218</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>532480</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7160773</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129995742</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>532090</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7160513</v>
+      </c>
+      <c r="S79" t="n">
+        <v>2</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129995764</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>532551</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7160541</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129995746</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91622</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>532167</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7160611</v>
+      </c>
+      <c r="S81" t="n">
+        <v>2</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129995754</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80224</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>532432</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7160793</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129995783</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Pissfisktjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>532391</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7160666</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dorotea</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Fastighetsverket NVB 2024</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>129995737</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
         <v>129995736</v>
       </c>
       <c r="B37" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5044,16 +5044,16 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129995760</v>
+        <v>129995741</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5061,42 +5061,33 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532511</v>
+        <v>532146</v>
       </c>
       <c r="R38" t="n">
-        <v>7160701</v>
+        <v>7160573</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5150,7 +5141,7 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5150,7 @@
         <v>129995772</v>
       </c>
       <c r="B39" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5251,16 +5242,16 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995741</v>
+        <v>129995760</v>
       </c>
       <c r="B40" t="n">
-        <v>91622</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5268,33 +5259,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532146</v>
+        <v>532511</v>
       </c>
       <c r="R40" t="n">
-        <v>7160573</v>
+        <v>7160701</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5348,38 +5348,38 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>80093</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R41" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5449,38 +5449,38 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>80096</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R42" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
         <v>129995776</v>
       </c>
       <c r="B43" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5651,16 +5651,16 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995770</v>
+        <v>129995739</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>91625</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,42 +5668,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532587</v>
+        <v>532158</v>
       </c>
       <c r="R44" t="n">
-        <v>7160733</v>
+        <v>7160507</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5757,36 +5748,40 @@
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995739</v>
+        <v>129995744</v>
       </c>
       <c r="B45" t="n">
-        <v>91622</v>
+        <v>80221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5794,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532158</v>
+        <v>532040</v>
       </c>
       <c r="R45" t="n">
-        <v>7160507</v>
+        <v>7160538</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5854,16 +5849,16 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995744</v>
+        <v>129995763</v>
       </c>
       <c r="B46" t="n">
-        <v>80218</v>
+        <v>80227</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5871,21 +5866,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5895,13 +5890,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532040</v>
+        <v>532539</v>
       </c>
       <c r="R46" t="n">
-        <v>7160538</v>
+        <v>7160707</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5955,16 +5950,16 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995763</v>
+        <v>129995766</v>
       </c>
       <c r="B47" t="n">
-        <v>80224</v>
+        <v>80228</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5972,21 +5967,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5996,10 +5991,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532539</v>
+        <v>532620</v>
       </c>
       <c r="R47" t="n">
-        <v>7160707</v>
+        <v>7160493</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6056,16 +6051,16 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995766</v>
+        <v>129995780</v>
       </c>
       <c r="B48" t="n">
-        <v>80225</v>
+        <v>80227</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6073,21 +6068,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6097,13 +6092,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532620</v>
+        <v>532432</v>
       </c>
       <c r="R48" t="n">
-        <v>7160493</v>
+        <v>7160802</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6157,54 +6152,59 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995780</v>
+        <v>129995770</v>
       </c>
       <c r="B49" t="n">
-        <v>80224</v>
+        <v>57740</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532432</v>
+        <v>532587</v>
       </c>
       <c r="R49" t="n">
-        <v>7160802</v>
+        <v>7160733</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6258,16 +6258,16 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995750</v>
+        <v>129995747</v>
       </c>
       <c r="B50" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532257</v>
+        <v>532181</v>
       </c>
       <c r="R50" t="n">
-        <v>7160770</v>
+        <v>7160703</v>
       </c>
       <c r="S50" t="n">
         <v>2</v>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
         <v>129995748</v>
       </c>
       <c r="B51" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6452,16 +6452,16 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995747</v>
+        <v>129995750</v>
       </c>
       <c r="B52" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532181</v>
+        <v>532257</v>
       </c>
       <c r="R52" t="n">
-        <v>7160703</v>
+        <v>7160770</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
         <v>129995767</v>
       </c>
       <c r="B53" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
         <v>129995757</v>
       </c>
       <c r="B54" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6747,16 +6747,16 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995755</v>
+        <v>129995771</v>
       </c>
       <c r="B55" t="n">
-        <v>78841</v>
+        <v>91625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,23 +6764,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6788,13 +6784,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532399</v>
+        <v>532562</v>
       </c>
       <c r="R55" t="n">
-        <v>7160737</v>
+        <v>7160754</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6848,16 +6844,16 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995769</v>
+        <v>129995753</v>
       </c>
       <c r="B56" t="n">
-        <v>80224</v>
+        <v>80221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6861,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,13 +6885,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532626</v>
+        <v>532432</v>
       </c>
       <c r="R56" t="n">
-        <v>7160718</v>
+        <v>7160788</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6949,16 +6945,16 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995759</v>
+        <v>129995755</v>
       </c>
       <c r="B57" t="n">
-        <v>80190</v>
+        <v>78844</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6966,21 +6962,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,10 +6986,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532498</v>
+        <v>532399</v>
       </c>
       <c r="R57" t="n">
-        <v>7160682</v>
+        <v>7160737</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7050,7 +7046,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7055,7 @@
         <v>129995745</v>
       </c>
       <c r="B58" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,38 +7152,38 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995753</v>
+        <v>129995759</v>
       </c>
       <c r="B59" t="n">
-        <v>80218</v>
+        <v>80193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7197,13 +7193,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532432</v>
+        <v>532498</v>
       </c>
       <c r="R59" t="n">
-        <v>7160788</v>
+        <v>7160682</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7257,7 +7253,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7262,7 @@
         <v>129995762</v>
       </c>
       <c r="B60" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7358,36 +7354,40 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995771</v>
+        <v>129995769</v>
       </c>
       <c r="B61" t="n">
-        <v>91622</v>
+        <v>80227</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7395,13 +7395,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532562</v>
+        <v>532626</v>
       </c>
       <c r="R61" t="n">
-        <v>7160754</v>
+        <v>7160718</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
         <v>129995756</v>
       </c>
       <c r="B62" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         <v>129995779</v>
       </c>
       <c r="B63" t="n">
-        <v>80093</v>
+        <v>80096</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7657,51 +7657,56 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995774</v>
+        <v>129995777</v>
       </c>
       <c r="B64" t="n">
-        <v>80224</v>
+        <v>57740</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532519</v>
+        <v>532500</v>
       </c>
       <c r="R64" t="n">
-        <v>7160765</v>
+        <v>7160787</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7758,56 +7763,51 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995777</v>
+        <v>129995774</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>80227</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532500</v>
+        <v>532519</v>
       </c>
       <c r="R65" t="n">
-        <v>7160787</v>
+        <v>7160765</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7864,7 +7864,7 @@
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
         <v>129995775</v>
       </c>
       <c r="B66" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7965,38 +7965,38 @@
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995782</v>
+        <v>129995768</v>
       </c>
       <c r="B67" t="n">
-        <v>79703</v>
+        <v>80096</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532409</v>
+        <v>532602</v>
       </c>
       <c r="R67" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8066,16 +8066,16 @@
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995773</v>
+        <v>129995782</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8083,42 +8083,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532558</v>
+        <v>532409</v>
       </c>
       <c r="R68" t="n">
-        <v>7160752</v>
+        <v>7160698</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8172,7 +8167,7 @@
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8176,7 @@
         <v>129995758</v>
       </c>
       <c r="B69" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,54 +8268,59 @@
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995798</v>
+        <v>129995773</v>
       </c>
       <c r="B70" t="n">
-        <v>98815</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532493</v>
+        <v>532558</v>
       </c>
       <c r="R70" t="n">
-        <v>7160688</v>
+        <v>7160752</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8344,12 +8344,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8369,21 +8369,21 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129995768</v>
+        <v>129995798</v>
       </c>
       <c r="B71" t="n">
-        <v>80093</v>
+        <v>98818</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,21 +8391,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8415,13 +8415,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532602</v>
+        <v>532493</v>
       </c>
       <c r="R71" t="n">
-        <v>7160718</v>
+        <v>7160688</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8470,12 +8470,12 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
         <v>129995751</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
         <v>129995735</v>
       </c>
       <c r="B73" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8682,16 +8682,16 @@
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995738</v>
+        <v>129995743</v>
       </c>
       <c r="B74" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532209</v>
+        <v>532052</v>
       </c>
       <c r="R74" t="n">
-        <v>7160509</v>
+        <v>7160499</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8783,16 +8783,16 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995743</v>
+        <v>129995738</v>
       </c>
       <c r="B75" t="n">
-        <v>80218</v>
+        <v>80221</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532052</v>
+        <v>532209</v>
       </c>
       <c r="R75" t="n">
-        <v>7160499</v>
+        <v>7160509</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8884,59 +8884,54 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>80221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R76" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8990,56 +8985,51 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995749</v>
+        <v>129995742</v>
       </c>
       <c r="B77" t="n">
-        <v>57737</v>
+        <v>80228</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532259</v>
+        <v>532090</v>
       </c>
       <c r="R77" t="n">
-        <v>7160727</v>
+        <v>7160513</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9096,51 +9086,56 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995778</v>
+        <v>129995749</v>
       </c>
       <c r="B78" t="n">
-        <v>80218</v>
+        <v>57740</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532480</v>
+        <v>532259</v>
       </c>
       <c r="R78" t="n">
-        <v>7160773</v>
+        <v>7160727</v>
       </c>
       <c r="S78" t="n">
         <v>2</v>
@@ -9197,54 +9192,59 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995742</v>
+        <v>129995740</v>
       </c>
       <c r="B79" t="n">
-        <v>80225</v>
+        <v>57740</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532090</v>
+        <v>532123</v>
       </c>
       <c r="R79" t="n">
-        <v>7160513</v>
+        <v>7160541</v>
       </c>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9298,16 +9298,16 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129995764</v>
+        <v>129995746</v>
       </c>
       <c r="B80" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532551</v>
+        <v>532167</v>
       </c>
       <c r="R80" t="n">
-        <v>7160541</v>
+        <v>7160611</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9395,16 +9395,16 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129995746</v>
+        <v>129995764</v>
       </c>
       <c r="B81" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9432,13 +9432,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532167</v>
+        <v>532551</v>
       </c>
       <c r="R81" t="n">
-        <v>7160611</v>
+        <v>7160541</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -9501,7 +9501,7 @@
         <v>129995754</v>
       </c>
       <c r="B82" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
         <v>129995783</v>
       </c>
       <c r="B83" t="n">
-        <v>80149</v>
+        <v>80152</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>Fastighetsverket NVB 2024</t>
+          <t>Fastighetsverket NVB 2024 och 2025</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4847,10 +4847,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129995737</v>
+        <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4858,42 +4858,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532200</v>
+        <v>532620</v>
       </c>
       <c r="R36" t="n">
         <v>7160691</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4953,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129995736</v>
+        <v>129995737</v>
       </c>
       <c r="B37" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4964,33 +4955,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532620</v>
+        <v>532200</v>
       </c>
       <c r="R37" t="n">
         <v>7160691</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995771</v>
+        <v>129995759</v>
       </c>
       <c r="B55" t="n">
-        <v>91625</v>
+        <v>80193</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,19 +6764,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6784,13 +6788,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532562</v>
+        <v>532498</v>
       </c>
       <c r="R55" t="n">
-        <v>7160754</v>
+        <v>7160682</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6951,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995755</v>
+        <v>129995762</v>
       </c>
       <c r="B57" t="n">
-        <v>78844</v>
+        <v>80221</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532399</v>
+        <v>532540</v>
       </c>
       <c r="R57" t="n">
-        <v>7160737</v>
+        <v>7160698</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995745</v>
+        <v>129995771</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7063,42 +7067,33 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532176</v>
+        <v>532562</v>
       </c>
       <c r="R58" t="n">
-        <v>7160588</v>
+        <v>7160754</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7158,10 +7153,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995759</v>
+        <v>129995755</v>
       </c>
       <c r="B59" t="n">
-        <v>80193</v>
+        <v>78844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7193,10 +7188,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532498</v>
+        <v>532399</v>
       </c>
       <c r="R59" t="n">
-        <v>7160682</v>
+        <v>7160737</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7259,10 +7254,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995762</v>
+        <v>129995769</v>
       </c>
       <c r="B60" t="n">
-        <v>80221</v>
+        <v>80227</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7270,21 +7265,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7294,13 +7289,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532540</v>
+        <v>532626</v>
       </c>
       <c r="R60" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7360,48 +7355,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995769</v>
+        <v>129995745</v>
       </c>
       <c r="B61" t="n">
-        <v>80227</v>
+        <v>57740</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532626</v>
+        <v>532176</v>
       </c>
       <c r="R61" t="n">
-        <v>7160718</v>
+        <v>7160588</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995743</v>
+        <v>129995738</v>
       </c>
       <c r="B74" t="n">
         <v>80221</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532052</v>
+        <v>532209</v>
       </c>
       <c r="R74" t="n">
-        <v>7160499</v>
+        <v>7160509</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8789,7 +8789,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995738</v>
+        <v>129995743</v>
       </c>
       <c r="B75" t="n">
         <v>80221</v>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532209</v>
+        <v>532052</v>
       </c>
       <c r="R75" t="n">
-        <v>7160509</v>
+        <v>7160499</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -5050,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129995741</v>
+        <v>129995760</v>
       </c>
       <c r="B38" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5061,33 +5061,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532146</v>
+        <v>532511</v>
       </c>
       <c r="R38" t="n">
-        <v>7160573</v>
+        <v>7160701</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5248,10 +5257,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995760</v>
+        <v>129995741</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>91625</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,42 +5268,33 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532511</v>
+        <v>532146</v>
       </c>
       <c r="R40" t="n">
-        <v>7160701</v>
+        <v>7160573</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -6264,30 +6264,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995747</v>
+        <v>129995757</v>
       </c>
       <c r="B50" t="n">
-        <v>91625</v>
+        <v>80228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6295,13 +6299,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532181</v>
+        <v>532504</v>
       </c>
       <c r="R50" t="n">
-        <v>7160703</v>
+        <v>7160709</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,7 +6365,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995748</v>
+        <v>129995747</v>
       </c>
       <c r="B51" t="n">
         <v>91625</v>
@@ -6392,13 +6396,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532226</v>
+        <v>532181</v>
       </c>
       <c r="R51" t="n">
-        <v>7160724</v>
+        <v>7160703</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6458,7 +6462,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995750</v>
+        <v>129995748</v>
       </c>
       <c r="B52" t="n">
         <v>91625</v>
@@ -6489,13 +6493,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532257</v>
+        <v>532226</v>
       </c>
       <c r="R52" t="n">
-        <v>7160770</v>
+        <v>7160724</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6555,7 +6559,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995767</v>
+        <v>129995750</v>
       </c>
       <c r="B53" t="n">
         <v>91625</v>
@@ -6586,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532608</v>
+        <v>532257</v>
       </c>
       <c r="R53" t="n">
-        <v>7160642</v>
+        <v>7160770</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6652,34 +6656,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995757</v>
+        <v>129995767</v>
       </c>
       <c r="B54" t="n">
-        <v>80228</v>
+        <v>91625</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532504</v>
+        <v>532608</v>
       </c>
       <c r="R54" t="n">
-        <v>7160709</v>
+        <v>7160642</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995759</v>
+        <v>129995771</v>
       </c>
       <c r="B55" t="n">
-        <v>80193</v>
+        <v>91625</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,23 +6764,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6788,13 +6784,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532498</v>
+        <v>532562</v>
       </c>
       <c r="R55" t="n">
-        <v>7160682</v>
+        <v>7160754</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6955,32 +6951,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995762</v>
+        <v>129995755</v>
       </c>
       <c r="B57" t="n">
-        <v>80221</v>
+        <v>78844</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,13 +6986,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532540</v>
+        <v>532399</v>
       </c>
       <c r="R57" t="n">
-        <v>7160698</v>
+        <v>7160737</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7056,10 +7052,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995771</v>
+        <v>129995745</v>
       </c>
       <c r="B58" t="n">
-        <v>91625</v>
+        <v>57740</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,33 +7063,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532562</v>
+        <v>532176</v>
       </c>
       <c r="R58" t="n">
-        <v>7160754</v>
+        <v>7160588</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7153,10 +7158,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995755</v>
+        <v>129995759</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>80193</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7164,21 +7169,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7188,10 +7193,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532399</v>
+        <v>532498</v>
       </c>
       <c r="R59" t="n">
-        <v>7160737</v>
+        <v>7160682</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7254,10 +7259,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995769</v>
+        <v>129995762</v>
       </c>
       <c r="B60" t="n">
-        <v>80227</v>
+        <v>80221</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7265,21 +7270,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7289,13 +7294,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532626</v>
+        <v>532540</v>
       </c>
       <c r="R60" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7355,53 +7360,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995745</v>
+        <v>129995769</v>
       </c>
       <c r="B61" t="n">
-        <v>57740</v>
+        <v>80227</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532176</v>
+        <v>532626</v>
       </c>
       <c r="R61" t="n">
-        <v>7160588</v>
+        <v>7160718</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7562,10 +7562,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995779</v>
+        <v>129995774</v>
       </c>
       <c r="B63" t="n">
-        <v>80096</v>
+        <v>80227</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7573,21 +7573,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532445</v>
+        <v>532519</v>
       </c>
       <c r="R63" t="n">
-        <v>7160791</v>
+        <v>7160765</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7663,53 +7663,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995777</v>
+        <v>129995775</v>
       </c>
       <c r="B64" t="n">
-        <v>57740</v>
+        <v>80221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532500</v>
+        <v>532521</v>
       </c>
       <c r="R64" t="n">
-        <v>7160787</v>
+        <v>7160766</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7769,45 +7764,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995774</v>
+        <v>129995777</v>
       </c>
       <c r="B65" t="n">
-        <v>80227</v>
+        <v>57740</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532519</v>
+        <v>532500</v>
       </c>
       <c r="R65" t="n">
-        <v>7160765</v>
+        <v>7160787</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995775</v>
+        <v>129995779</v>
       </c>
       <c r="B66" t="n">
-        <v>80221</v>
+        <v>80096</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7905,13 +7905,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532521</v>
+        <v>532445</v>
       </c>
       <c r="R66" t="n">
-        <v>7160766</v>
+        <v>7160791</v>
       </c>
       <c r="S66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5159,7 +5159,7 @@
         <v>129995772</v>
       </c>
       <c r="B39" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>129995741</v>
       </c>
       <c r="B40" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>80096</v>
+        <v>80097</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>129995776</v>
       </c>
       <c r="B43" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,30 +5657,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995739</v>
+        <v>129995763</v>
       </c>
       <c r="B44" t="n">
-        <v>91625</v>
+        <v>80228</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5688,13 +5692,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532158</v>
+        <v>532539</v>
       </c>
       <c r="R44" t="n">
-        <v>7160507</v>
+        <v>7160707</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5754,10 +5758,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995744</v>
+        <v>129995766</v>
       </c>
       <c r="B45" t="n">
-        <v>80221</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5765,21 +5769,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5789,13 +5793,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532040</v>
+        <v>532620</v>
       </c>
       <c r="R45" t="n">
-        <v>7160538</v>
+        <v>7160493</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5855,10 +5859,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995763</v>
+        <v>129995780</v>
       </c>
       <c r="B46" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5890,13 +5894,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532539</v>
+        <v>532432</v>
       </c>
       <c r="R46" t="n">
-        <v>7160707</v>
+        <v>7160802</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5956,34 +5960,30 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995766</v>
+        <v>129995739</v>
       </c>
       <c r="B47" t="n">
-        <v>80228</v>
+        <v>91626</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532620</v>
+        <v>532158</v>
       </c>
       <c r="R47" t="n">
-        <v>7160493</v>
+        <v>7160507</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6057,10 +6057,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995780</v>
+        <v>129995744</v>
       </c>
       <c r="B48" t="n">
-        <v>80227</v>
+        <v>80222</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,21 +6068,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532432</v>
+        <v>532040</v>
       </c>
       <c r="R48" t="n">
-        <v>7160802</v>
+        <v>7160538</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6264,34 +6264,30 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995757</v>
+        <v>129995748</v>
       </c>
       <c r="B50" t="n">
-        <v>80228</v>
+        <v>91626</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6299,13 +6295,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532504</v>
+        <v>532226</v>
       </c>
       <c r="R50" t="n">
-        <v>7160709</v>
+        <v>7160724</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6368,7 +6364,7 @@
         <v>129995747</v>
       </c>
       <c r="B51" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6462,10 +6458,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995748</v>
+        <v>129995767</v>
       </c>
       <c r="B52" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6493,13 +6489,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532226</v>
+        <v>532608</v>
       </c>
       <c r="R52" t="n">
-        <v>7160724</v>
+        <v>7160642</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6559,30 +6555,34 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995750</v>
+        <v>129995757</v>
       </c>
       <c r="B53" t="n">
-        <v>91625</v>
+        <v>80229</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6590,13 +6590,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532257</v>
+        <v>532504</v>
       </c>
       <c r="R53" t="n">
-        <v>7160770</v>
+        <v>7160709</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995767</v>
+        <v>129995750</v>
       </c>
       <c r="B54" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532608</v>
+        <v>532257</v>
       </c>
       <c r="R54" t="n">
-        <v>7160642</v>
+        <v>7160770</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995771</v>
+        <v>129995755</v>
       </c>
       <c r="B55" t="n">
-        <v>91625</v>
+        <v>78845</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,19 +6764,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6784,13 +6788,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532562</v>
+        <v>532399</v>
       </c>
       <c r="R55" t="n">
-        <v>7160754</v>
+        <v>7160737</v>
       </c>
       <c r="S55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6853,7 +6857,7 @@
         <v>129995753</v>
       </c>
       <c r="B56" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6951,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995755</v>
+        <v>129995762</v>
       </c>
       <c r="B57" t="n">
-        <v>78844</v>
+        <v>80222</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6986,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532399</v>
+        <v>532540</v>
       </c>
       <c r="R57" t="n">
-        <v>7160737</v>
+        <v>7160698</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995745</v>
+        <v>129995759</v>
       </c>
       <c r="B58" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7063,42 +7067,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532176</v>
+        <v>532498</v>
       </c>
       <c r="R58" t="n">
-        <v>7160588</v>
+        <v>7160682</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7158,32 +7157,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995759</v>
+        <v>129995769</v>
       </c>
       <c r="B59" t="n">
-        <v>80193</v>
+        <v>80228</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7193,10 +7192,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532498</v>
+        <v>532626</v>
       </c>
       <c r="R59" t="n">
-        <v>7160682</v>
+        <v>7160718</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7259,34 +7258,30 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995762</v>
+        <v>129995771</v>
       </c>
       <c r="B60" t="n">
-        <v>80221</v>
+        <v>91626</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7294,10 +7289,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532540</v>
+        <v>532562</v>
       </c>
       <c r="R60" t="n">
-        <v>7160698</v>
+        <v>7160754</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -7360,48 +7355,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995769</v>
+        <v>129995745</v>
       </c>
       <c r="B61" t="n">
-        <v>80227</v>
+        <v>57740</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532626</v>
+        <v>532176</v>
       </c>
       <c r="R61" t="n">
-        <v>7160718</v>
+        <v>7160588</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>129995756</v>
       </c>
       <c r="B62" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,10 +7562,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995774</v>
+        <v>129995779</v>
       </c>
       <c r="B63" t="n">
-        <v>80227</v>
+        <v>80097</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7573,21 +7573,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532519</v>
+        <v>532445</v>
       </c>
       <c r="R63" t="n">
-        <v>7160765</v>
+        <v>7160791</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>129995775</v>
       </c>
       <c r="B64" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7764,50 +7764,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995777</v>
+        <v>129995774</v>
       </c>
       <c r="B65" t="n">
-        <v>57740</v>
+        <v>80228</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532500</v>
+        <v>532519</v>
       </c>
       <c r="R65" t="n">
-        <v>7160787</v>
+        <v>7160765</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7870,48 +7865,53 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995779</v>
+        <v>129995777</v>
       </c>
       <c r="B66" t="n">
-        <v>80096</v>
+        <v>57740</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532445</v>
+        <v>532500</v>
       </c>
       <c r="R66" t="n">
-        <v>7160791</v>
+        <v>7160787</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7971,45 +7971,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995768</v>
+        <v>129995773</v>
       </c>
       <c r="B67" t="n">
-        <v>80096</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532602</v>
+        <v>532558</v>
       </c>
       <c r="R67" t="n">
-        <v>7160718</v>
+        <v>7160752</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8072,32 +8077,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995782</v>
+        <v>129995768</v>
       </c>
       <c r="B68" t="n">
-        <v>79706</v>
+        <v>80097</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8112,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532409</v>
+        <v>532602</v>
       </c>
       <c r="R68" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8173,10 +8178,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995758</v>
+        <v>129995782</v>
       </c>
       <c r="B69" t="n">
-        <v>80192</v>
+        <v>79707</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8184,21 +8189,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8208,13 +8213,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532501</v>
+        <v>532409</v>
       </c>
       <c r="R69" t="n">
-        <v>7160693</v>
+        <v>7160698</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8274,10 +8279,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995773</v>
+        <v>129995758</v>
       </c>
       <c r="B70" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8285,39 +8290,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532558</v>
+        <v>532501</v>
       </c>
       <c r="R70" t="n">
-        <v>7160752</v>
+        <v>7160693</v>
       </c>
       <c r="S70" t="n">
         <v>2</v>
@@ -8383,7 +8383,7 @@
         <v>129995798</v>
       </c>
       <c r="B71" t="n">
-        <v>98818</v>
+        <v>98819</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129995735</v>
+        <v>129995738</v>
       </c>
       <c r="B73" t="n">
-        <v>91626</v>
+        <v>80222</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532609</v>
+        <v>532209</v>
       </c>
       <c r="R73" t="n">
-        <v>7160604</v>
+        <v>7160509</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8688,10 +8688,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995738</v>
+        <v>129995743</v>
       </c>
       <c r="B74" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532209</v>
+        <v>532052</v>
       </c>
       <c r="R74" t="n">
-        <v>7160509</v>
+        <v>7160499</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8789,32 +8789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995743</v>
+        <v>129995735</v>
       </c>
       <c r="B75" t="n">
-        <v>80221</v>
+        <v>91627</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532052</v>
+        <v>532609</v>
       </c>
       <c r="R75" t="n">
-        <v>7160499</v>
+        <v>7160604</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8893,7 +8893,7 @@
         <v>129995778</v>
       </c>
       <c r="B76" t="n">
-        <v>80221</v>
+        <v>80222</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>129995742</v>
       </c>
       <c r="B77" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995749</v>
+        <v>129995740</v>
       </c>
       <c r="B78" t="n">
         <v>57740</v>
@@ -9123,7 +9123,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9132,13 +9132,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532259</v>
+        <v>532123</v>
       </c>
       <c r="R78" t="n">
-        <v>7160727</v>
+        <v>7160541</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995740</v>
+        <v>129995749</v>
       </c>
       <c r="B79" t="n">
         <v>57740</v>
@@ -9229,7 +9229,7 @@
       <c r="I79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9238,13 +9238,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532123</v>
+        <v>532259</v>
       </c>
       <c r="R79" t="n">
-        <v>7160541</v>
+        <v>7160727</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9304,10 +9304,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129995746</v>
+        <v>129995764</v>
       </c>
       <c r="B80" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532167</v>
+        <v>532551</v>
       </c>
       <c r="R80" t="n">
-        <v>7160611</v>
+        <v>7160541</v>
       </c>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9401,10 +9401,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129995764</v>
+        <v>129995746</v>
       </c>
       <c r="B81" t="n">
-        <v>91625</v>
+        <v>91626</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9432,13 +9432,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532551</v>
+        <v>532167</v>
       </c>
       <c r="R81" t="n">
-        <v>7160541</v>
+        <v>7160611</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129995754</v>
       </c>
       <c r="B82" t="n">
-        <v>80227</v>
+        <v>80228</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>129995783</v>
       </c>
       <c r="B83" t="n">
-        <v>80152</v>
+        <v>80153</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -5156,10 +5156,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995772</v>
+        <v>129995741</v>
       </c>
       <c r="B39" t="n">
-        <v>91606</v>
+        <v>91626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5167,23 +5167,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5191,13 +5187,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532563</v>
+        <v>532146</v>
       </c>
       <c r="R39" t="n">
-        <v>7160749</v>
+        <v>7160573</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5257,10 +5253,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995741</v>
+        <v>129995772</v>
       </c>
       <c r="B40" t="n">
-        <v>91626</v>
+        <v>91606</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5268,19 +5264,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532146</v>
+        <v>532563</v>
       </c>
       <c r="R40" t="n">
-        <v>7160573</v>
+        <v>7160749</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>80097</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R41" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B42" t="n">
-        <v>80097</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R42" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -7971,50 +7971,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995773</v>
+        <v>129995768</v>
       </c>
       <c r="B67" t="n">
-        <v>57740</v>
+        <v>80097</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532558</v>
+        <v>532602</v>
       </c>
       <c r="R67" t="n">
-        <v>7160752</v>
+        <v>7160718</v>
       </c>
       <c r="S67" t="n">
         <v>2</v>
@@ -8077,32 +8072,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995768</v>
+        <v>129995782</v>
       </c>
       <c r="B68" t="n">
-        <v>80097</v>
+        <v>79707</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8112,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532602</v>
+        <v>532409</v>
       </c>
       <c r="R68" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8178,10 +8173,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995782</v>
+        <v>129995758</v>
       </c>
       <c r="B69" t="n">
-        <v>79707</v>
+        <v>80193</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8189,21 +8184,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8213,13 +8208,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532409</v>
+        <v>532501</v>
       </c>
       <c r="R69" t="n">
-        <v>7160698</v>
+        <v>7160693</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8279,32 +8274,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995758</v>
+        <v>129995798</v>
       </c>
       <c r="B70" t="n">
-        <v>80193</v>
+        <v>98819</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8314,13 +8309,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532501</v>
+        <v>532493</v>
       </c>
       <c r="R70" t="n">
-        <v>7160693</v>
+        <v>7160688</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8344,12 +8339,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8369,7 +8364,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8380,48 +8375,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129995798</v>
+        <v>129995773</v>
       </c>
       <c r="B71" t="n">
-        <v>98819</v>
+        <v>57740</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532493</v>
+        <v>532558</v>
       </c>
       <c r="R71" t="n">
-        <v>7160688</v>
+        <v>7160752</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9304,7 +9304,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129995764</v>
+        <v>129995746</v>
       </c>
       <c r="B80" t="n">
         <v>91626</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532551</v>
+        <v>532167</v>
       </c>
       <c r="R80" t="n">
-        <v>7160541</v>
+        <v>7160611</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129995746</v>
+        <v>129995764</v>
       </c>
       <c r="B81" t="n">
         <v>91626</v>
@@ -9432,13 +9432,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532167</v>
+        <v>532551</v>
       </c>
       <c r="R81" t="n">
-        <v>7160611</v>
+        <v>7160541</v>
       </c>
       <c r="S81" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>80097</v>
+        <v>79088</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R41" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>80097</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R42" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995768</v>
+        <v>129995798</v>
       </c>
       <c r="B67" t="n">
-        <v>80097</v>
+        <v>98819</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7982,21 +7982,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532602</v>
+        <v>532493</v>
       </c>
       <c r="R67" t="n">
-        <v>7160718</v>
+        <v>7160688</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8072,32 +8072,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995782</v>
+        <v>129995768</v>
       </c>
       <c r="B68" t="n">
-        <v>79707</v>
+        <v>80097</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532409</v>
+        <v>532602</v>
       </c>
       <c r="R68" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8173,10 +8173,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995758</v>
+        <v>129995782</v>
       </c>
       <c r="B69" t="n">
-        <v>80193</v>
+        <v>79707</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8184,21 +8184,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8208,13 +8208,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532501</v>
+        <v>532409</v>
       </c>
       <c r="R69" t="n">
-        <v>7160693</v>
+        <v>7160698</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8274,32 +8274,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995798</v>
+        <v>129995758</v>
       </c>
       <c r="B70" t="n">
-        <v>98819</v>
+        <v>80193</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8309,13 +8309,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532493</v>
+        <v>532501</v>
       </c>
       <c r="R70" t="n">
-        <v>7160688</v>
+        <v>7160693</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8339,12 +8339,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -9304,7 +9304,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129995746</v>
+        <v>129995764</v>
       </c>
       <c r="B80" t="n">
         <v>91626</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>532167</v>
+        <v>532551</v>
       </c>
       <c r="R80" t="n">
-        <v>7160611</v>
+        <v>7160541</v>
       </c>
       <c r="S80" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129995764</v>
+        <v>129995746</v>
       </c>
       <c r="B81" t="n">
         <v>91626</v>
@@ -9432,13 +9432,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>532551</v>
+        <v>532167</v>
       </c>
       <c r="R81" t="n">
-        <v>7160541</v>
+        <v>7160611</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995741</v>
+        <v>129995772</v>
       </c>
       <c r="B39" t="n">
-        <v>91626</v>
+        <v>91623</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5167,19 +5167,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5187,13 +5191,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532146</v>
+        <v>532563</v>
       </c>
       <c r="R39" t="n">
-        <v>7160573</v>
+        <v>7160749</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5253,10 +5257,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995772</v>
+        <v>129995741</v>
       </c>
       <c r="B40" t="n">
-        <v>91606</v>
+        <v>91643</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5264,23 +5268,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532563</v>
+        <v>532146</v>
       </c>
       <c r="R40" t="n">
-        <v>7160749</v>
+        <v>7160573</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>129995776</v>
       </c>
       <c r="B43" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995763</v>
+        <v>129995744</v>
       </c>
       <c r="B44" t="n">
-        <v>80228</v>
+        <v>80223</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532539</v>
+        <v>532040</v>
       </c>
       <c r="R44" t="n">
-        <v>7160707</v>
+        <v>7160538</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995766</v>
+        <v>129995763</v>
       </c>
       <c r="B45" t="n">
         <v>80229</v>
@@ -5769,21 +5769,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532620</v>
+        <v>532539</v>
       </c>
       <c r="R45" t="n">
-        <v>7160493</v>
+        <v>7160707</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995780</v>
+        <v>129995766</v>
       </c>
       <c r="B46" t="n">
-        <v>80228</v>
+        <v>80230</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5870,21 +5870,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532432</v>
+        <v>532620</v>
       </c>
       <c r="R46" t="n">
-        <v>7160802</v>
+        <v>7160493</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5960,30 +5960,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995739</v>
+        <v>129995780</v>
       </c>
       <c r="B47" t="n">
-        <v>91626</v>
+        <v>80229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5991,10 +5995,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532158</v>
+        <v>532432</v>
       </c>
       <c r="R47" t="n">
-        <v>7160507</v>
+        <v>7160802</v>
       </c>
       <c r="S47" t="n">
         <v>2</v>
@@ -6057,34 +6061,30 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995744</v>
+        <v>129995739</v>
       </c>
       <c r="B48" t="n">
-        <v>80222</v>
+        <v>91643</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532040</v>
+        <v>532158</v>
       </c>
       <c r="R48" t="n">
-        <v>7160538</v>
+        <v>7160507</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6264,10 +6264,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995748</v>
+        <v>129995750</v>
       </c>
       <c r="B50" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6295,13 +6295,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532226</v>
+        <v>532257</v>
       </c>
       <c r="R50" t="n">
-        <v>7160724</v>
+        <v>7160770</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,10 +6361,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995747</v>
+        <v>129995748</v>
       </c>
       <c r="B51" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6392,13 +6392,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532181</v>
+        <v>532226</v>
       </c>
       <c r="R51" t="n">
-        <v>7160703</v>
+        <v>7160724</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995767</v>
+        <v>129995747</v>
       </c>
       <c r="B52" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532608</v>
+        <v>532181</v>
       </c>
       <c r="R52" t="n">
-        <v>7160642</v>
+        <v>7160703</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
@@ -6555,34 +6555,30 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995757</v>
+        <v>129995767</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>91643</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6590,13 +6586,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532504</v>
+        <v>532608</v>
       </c>
       <c r="R53" t="n">
-        <v>7160709</v>
+        <v>7160642</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6656,30 +6652,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995750</v>
+        <v>129995757</v>
       </c>
       <c r="B54" t="n">
-        <v>91626</v>
+        <v>80230</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532257</v>
+        <v>532504</v>
       </c>
       <c r="R54" t="n">
-        <v>7160770</v>
+        <v>7160709</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995755</v>
+        <v>129995759</v>
       </c>
       <c r="B55" t="n">
-        <v>78845</v>
+        <v>80195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,21 +6764,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532399</v>
+        <v>532498</v>
       </c>
       <c r="R55" t="n">
-        <v>7160737</v>
+        <v>7160682</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6854,45 +6854,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995753</v>
+        <v>129995745</v>
       </c>
       <c r="B56" t="n">
-        <v>80222</v>
+        <v>57740</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532432</v>
+        <v>532176</v>
       </c>
       <c r="R56" t="n">
-        <v>7160788</v>
+        <v>7160588</v>
       </c>
       <c r="S56" t="n">
         <v>2</v>
@@ -6955,34 +6960,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995762</v>
+        <v>129995771</v>
       </c>
       <c r="B57" t="n">
-        <v>80222</v>
+        <v>91643</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6990,10 +6991,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532540</v>
+        <v>532562</v>
       </c>
       <c r="R57" t="n">
-        <v>7160698</v>
+        <v>7160754</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -7056,10 +7057,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995759</v>
+        <v>129995755</v>
       </c>
       <c r="B58" t="n">
-        <v>80194</v>
+        <v>78846</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7067,21 +7068,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7091,10 +7092,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532498</v>
+        <v>532399</v>
       </c>
       <c r="R58" t="n">
-        <v>7160682</v>
+        <v>7160737</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7160,7 +7161,7 @@
         <v>129995769</v>
       </c>
       <c r="B59" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7258,30 +7259,34 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995771</v>
+        <v>129995753</v>
       </c>
       <c r="B60" t="n">
-        <v>91626</v>
+        <v>80223</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7289,13 +7294,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532562</v>
+        <v>532432</v>
       </c>
       <c r="R60" t="n">
-        <v>7160754</v>
+        <v>7160788</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7355,53 +7360,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995745</v>
+        <v>129995762</v>
       </c>
       <c r="B61" t="n">
-        <v>57740</v>
+        <v>80223</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532176</v>
+        <v>532540</v>
       </c>
       <c r="R61" t="n">
-        <v>7160588</v>
+        <v>7160698</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>129995756</v>
       </c>
       <c r="B62" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,48 +7562,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995779</v>
+        <v>129995777</v>
       </c>
       <c r="B63" t="n">
-        <v>80097</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532445</v>
+        <v>532500</v>
       </c>
       <c r="R63" t="n">
-        <v>7160791</v>
+        <v>7160787</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7663,10 +7668,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995775</v>
+        <v>129995779</v>
       </c>
       <c r="B64" t="n">
-        <v>80222</v>
+        <v>80098</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7674,21 +7679,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7698,13 +7703,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532521</v>
+        <v>532445</v>
       </c>
       <c r="R64" t="n">
-        <v>7160766</v>
+        <v>7160791</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7767,7 +7772,7 @@
         <v>129995774</v>
       </c>
       <c r="B65" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7865,53 +7870,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995777</v>
+        <v>129995775</v>
       </c>
       <c r="B66" t="n">
-        <v>57740</v>
+        <v>80223</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532500</v>
+        <v>532521</v>
       </c>
       <c r="R66" t="n">
-        <v>7160787</v>
+        <v>7160766</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7971,48 +7971,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995798</v>
+        <v>129995773</v>
       </c>
       <c r="B67" t="n">
-        <v>98819</v>
+        <v>57740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532493</v>
+        <v>532558</v>
       </c>
       <c r="R67" t="n">
-        <v>7160688</v>
+        <v>7160752</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8036,12 +8041,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,7 +8066,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8075,7 +8080,7 @@
         <v>129995768</v>
       </c>
       <c r="B68" t="n">
-        <v>80097</v>
+        <v>80098</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8176,7 +8181,7 @@
         <v>129995782</v>
       </c>
       <c r="B69" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8277,7 +8282,7 @@
         <v>129995758</v>
       </c>
       <c r="B70" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8375,53 +8380,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129995773</v>
+        <v>129995798</v>
       </c>
       <c r="B71" t="n">
-        <v>57740</v>
+        <v>98836</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532558</v>
+        <v>532493</v>
       </c>
       <c r="R71" t="n">
-        <v>7160752</v>
+        <v>7160688</v>
       </c>
       <c r="S71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8590,7 +8590,7 @@
         <v>129995738</v>
       </c>
       <c r="B73" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>129995743</v>
       </c>
       <c r="B74" t="n">
-        <v>80222</v>
+        <v>80223</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>129995735</v>
       </c>
       <c r="B75" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8890,48 +8890,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995778</v>
+        <v>129995740</v>
       </c>
       <c r="B76" t="n">
-        <v>80222</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532480</v>
+        <v>532123</v>
       </c>
       <c r="R76" t="n">
-        <v>7160773</v>
+        <v>7160541</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8991,45 +8996,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995742</v>
+        <v>129995749</v>
       </c>
       <c r="B77" t="n">
-        <v>80229</v>
+        <v>57740</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532090</v>
+        <v>532259</v>
       </c>
       <c r="R77" t="n">
-        <v>7160513</v>
+        <v>7160727</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9092,53 +9102,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B78" t="n">
-        <v>57740</v>
+        <v>80223</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R78" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9198,50 +9203,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995749</v>
+        <v>129995742</v>
       </c>
       <c r="B79" t="n">
-        <v>57740</v>
+        <v>80230</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532259</v>
+        <v>532090</v>
       </c>
       <c r="R79" t="n">
-        <v>7160727</v>
+        <v>7160513</v>
       </c>
       <c r="S79" t="n">
         <v>2</v>
@@ -9307,7 +9307,7 @@
         <v>129995764</v>
       </c>
       <c r="B80" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>129995746</v>
       </c>
       <c r="B81" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129995754</v>
       </c>
       <c r="B82" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>129995783</v>
       </c>
       <c r="B83" t="n">
-        <v>80153</v>
+        <v>80154</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -6264,34 +6264,30 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995757</v>
+        <v>129995750</v>
       </c>
       <c r="B50" t="n">
-        <v>80236</v>
+        <v>91659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6299,13 +6295,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532504</v>
+        <v>532257</v>
       </c>
       <c r="R50" t="n">
-        <v>7160709</v>
+        <v>7160770</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6365,7 +6361,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995750</v>
+        <v>129995748</v>
       </c>
       <c r="B51" t="n">
         <v>91659</v>
@@ -6396,13 +6392,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532257</v>
+        <v>532226</v>
       </c>
       <c r="R51" t="n">
-        <v>7160770</v>
+        <v>7160724</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6462,7 +6458,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995748</v>
+        <v>129995747</v>
       </c>
       <c r="B52" t="n">
         <v>91659</v>
@@ -6493,13 +6489,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532226</v>
+        <v>532181</v>
       </c>
       <c r="R52" t="n">
-        <v>7160724</v>
+        <v>7160703</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6559,7 +6555,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995747</v>
+        <v>129995767</v>
       </c>
       <c r="B53" t="n">
         <v>91659</v>
@@ -6590,10 +6586,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532181</v>
+        <v>532608</v>
       </c>
       <c r="R53" t="n">
-        <v>7160703</v>
+        <v>7160642</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6656,30 +6652,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995767</v>
+        <v>129995757</v>
       </c>
       <c r="B54" t="n">
-        <v>91659</v>
+        <v>80236</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532608</v>
+        <v>532504</v>
       </c>
       <c r="R54" t="n">
-        <v>7160642</v>
+        <v>7160709</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -6264,30 +6264,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995750</v>
+        <v>129995757</v>
       </c>
       <c r="B50" t="n">
-        <v>91659</v>
+        <v>80236</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6295,13 +6299,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532257</v>
+        <v>532504</v>
       </c>
       <c r="R50" t="n">
-        <v>7160770</v>
+        <v>7160709</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,7 +6365,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995748</v>
+        <v>129995750</v>
       </c>
       <c r="B51" t="n">
         <v>91659</v>
@@ -6392,13 +6396,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532226</v>
+        <v>532257</v>
       </c>
       <c r="R51" t="n">
-        <v>7160724</v>
+        <v>7160770</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6458,7 +6462,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995747</v>
+        <v>129995748</v>
       </c>
       <c r="B52" t="n">
         <v>91659</v>
@@ -6489,13 +6493,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532181</v>
+        <v>532226</v>
       </c>
       <c r="R52" t="n">
-        <v>7160703</v>
+        <v>7160724</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6555,7 +6559,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995767</v>
+        <v>129995747</v>
       </c>
       <c r="B53" t="n">
         <v>91659</v>
@@ -6586,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532608</v>
+        <v>532181</v>
       </c>
       <c r="R53" t="n">
-        <v>7160642</v>
+        <v>7160703</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6652,34 +6656,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995757</v>
+        <v>129995767</v>
       </c>
       <c r="B54" t="n">
-        <v>80236</v>
+        <v>91659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532504</v>
+        <v>532608</v>
       </c>
       <c r="R54" t="n">
-        <v>7160709</v>
+        <v>7160642</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995755</v>
+        <v>129995771</v>
       </c>
       <c r="B56" t="n">
-        <v>78852</v>
+        <v>91659</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,23 +6865,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6889,13 +6885,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532399</v>
+        <v>532562</v>
       </c>
       <c r="R56" t="n">
-        <v>7160737</v>
+        <v>7160754</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,53 +6951,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995745</v>
+        <v>129995769</v>
       </c>
       <c r="B57" t="n">
-        <v>57741</v>
+        <v>80235</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532176</v>
+        <v>532626</v>
       </c>
       <c r="R57" t="n">
-        <v>7160588</v>
+        <v>7160718</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7061,30 +7052,34 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995771</v>
+        <v>129995753</v>
       </c>
       <c r="B58" t="n">
-        <v>91659</v>
+        <v>80229</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7092,13 +7087,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532562</v>
+        <v>532432</v>
       </c>
       <c r="R58" t="n">
-        <v>7160754</v>
+        <v>7160788</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7158,10 +7153,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995769</v>
+        <v>129995762</v>
       </c>
       <c r="B59" t="n">
-        <v>80235</v>
+        <v>80229</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7169,21 +7164,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7193,13 +7188,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532626</v>
+        <v>532540</v>
       </c>
       <c r="R59" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7259,32 +7254,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995753</v>
+        <v>129995755</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>78852</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7294,13 +7289,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532432</v>
+        <v>532399</v>
       </c>
       <c r="R60" t="n">
-        <v>7160788</v>
+        <v>7160737</v>
       </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7360,48 +7355,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995762</v>
+        <v>129995745</v>
       </c>
       <c r="B61" t="n">
-        <v>80229</v>
+        <v>57741</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532540</v>
+        <v>532176</v>
       </c>
       <c r="R61" t="n">
-        <v>7160698</v>
+        <v>7160588</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995778</v>
+        <v>129995742</v>
       </c>
       <c r="B76" t="n">
-        <v>80229</v>
+        <v>80236</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532480</v>
+        <v>532090</v>
       </c>
       <c r="R76" t="n">
-        <v>7160773</v>
+        <v>7160513</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
@@ -8991,53 +8991,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B77" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R77" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9097,7 +9092,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995749</v>
+        <v>129995740</v>
       </c>
       <c r="B78" t="n">
         <v>57741</v>
@@ -9128,7 +9123,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9137,13 +9132,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532259</v>
+        <v>532123</v>
       </c>
       <c r="R78" t="n">
-        <v>7160727</v>
+        <v>7160541</v>
       </c>
       <c r="S78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9203,45 +9198,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995742</v>
+        <v>129995749</v>
       </c>
       <c r="B79" t="n">
-        <v>80236</v>
+        <v>57741</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532090</v>
+        <v>532259</v>
       </c>
       <c r="R79" t="n">
-        <v>7160513</v>
+        <v>7160727</v>
       </c>
       <c r="S79" t="n">
         <v>2</v>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>129995772</v>
       </c>
       <c r="B38" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129995741</v>
       </c>
       <c r="B39" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5657,30 +5657,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995739</v>
+        <v>129995763</v>
       </c>
       <c r="B44" t="n">
-        <v>91659</v>
+        <v>80235</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5688,13 +5692,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532158</v>
+        <v>532539</v>
       </c>
       <c r="R44" t="n">
-        <v>7160507</v>
+        <v>7160707</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5754,10 +5758,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995744</v>
+        <v>129995766</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>80236</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5765,21 +5769,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5789,13 +5793,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532040</v>
+        <v>532620</v>
       </c>
       <c r="R45" t="n">
-        <v>7160538</v>
+        <v>7160493</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5855,7 +5859,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995763</v>
+        <v>129995780</v>
       </c>
       <c r="B46" t="n">
         <v>80235</v>
@@ -5890,13 +5894,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532539</v>
+        <v>532432</v>
       </c>
       <c r="R46" t="n">
-        <v>7160707</v>
+        <v>7160802</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5956,45 +5960,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995766</v>
+        <v>129995770</v>
       </c>
       <c r="B47" t="n">
-        <v>80236</v>
+        <v>57741</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532620</v>
+        <v>532587</v>
       </c>
       <c r="R47" t="n">
-        <v>7160493</v>
+        <v>7160733</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6057,34 +6066,30 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995780</v>
+        <v>129995739</v>
       </c>
       <c r="B48" t="n">
-        <v>80235</v>
+        <v>91661</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6092,10 +6097,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532432</v>
+        <v>532158</v>
       </c>
       <c r="R48" t="n">
-        <v>7160802</v>
+        <v>7160507</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6158,53 +6163,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995770</v>
+        <v>129995744</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>80229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532587</v>
+        <v>532040</v>
       </c>
       <c r="R49" t="n">
-        <v>7160733</v>
+        <v>7160538</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v>129995750</v>
       </c>
       <c r="B51" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>129995748</v>
       </c>
       <c r="B52" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>129995747</v>
       </c>
       <c r="B53" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>129995767</v>
       </c>
       <c r="B54" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6854,30 +6854,34 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995771</v>
+        <v>129995769</v>
       </c>
       <c r="B56" t="n">
-        <v>91659</v>
+        <v>80235</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6885,13 +6889,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532562</v>
+        <v>532626</v>
       </c>
       <c r="R56" t="n">
-        <v>7160754</v>
+        <v>7160718</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6951,34 +6955,30 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995769</v>
+        <v>129995771</v>
       </c>
       <c r="B57" t="n">
-        <v>80235</v>
+        <v>91661</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6986,13 +6986,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532626</v>
+        <v>532562</v>
       </c>
       <c r="R57" t="n">
-        <v>7160718</v>
+        <v>7160754</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7052,32 +7052,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995753</v>
+        <v>129995755</v>
       </c>
       <c r="B58" t="n">
-        <v>80229</v>
+        <v>78852</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7087,13 +7087,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532432</v>
+        <v>532399</v>
       </c>
       <c r="R58" t="n">
-        <v>7160788</v>
+        <v>7160737</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995762</v>
+        <v>129995753</v>
       </c>
       <c r="B59" t="n">
         <v>80229</v>
@@ -7188,13 +7188,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532540</v>
+        <v>532432</v>
       </c>
       <c r="R59" t="n">
-        <v>7160698</v>
+        <v>7160788</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7254,32 +7254,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995755</v>
+        <v>129995762</v>
       </c>
       <c r="B60" t="n">
-        <v>78852</v>
+        <v>80229</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7289,13 +7289,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532399</v>
+        <v>532540</v>
       </c>
       <c r="R60" t="n">
-        <v>7160737</v>
+        <v>7160698</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7562,10 +7562,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995775</v>
+        <v>129995779</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>80104</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7573,21 +7573,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7597,13 +7597,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532521</v>
+        <v>532445</v>
       </c>
       <c r="R63" t="n">
-        <v>7160766</v>
+        <v>7160791</v>
       </c>
       <c r="S63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7663,10 +7663,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995779</v>
+        <v>129995775</v>
       </c>
       <c r="B64" t="n">
-        <v>80104</v>
+        <v>80229</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7674,21 +7674,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7698,13 +7698,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532445</v>
+        <v>532521</v>
       </c>
       <c r="R64" t="n">
-        <v>7160791</v>
+        <v>7160766</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7764,45 +7764,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995774</v>
+        <v>129995777</v>
       </c>
       <c r="B65" t="n">
-        <v>80235</v>
+        <v>57741</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532519</v>
+        <v>532500</v>
       </c>
       <c r="R65" t="n">
-        <v>7160765</v>
+        <v>7160787</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7865,50 +7870,45 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995777</v>
+        <v>129995774</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>80235</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532500</v>
+        <v>532519</v>
       </c>
       <c r="R66" t="n">
-        <v>7160787</v>
+        <v>7160765</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7971,32 +7971,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995782</v>
+        <v>129995768</v>
       </c>
       <c r="B67" t="n">
-        <v>79714</v>
+        <v>80104</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532409</v>
+        <v>532602</v>
       </c>
       <c r="R67" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8072,32 +8072,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995768</v>
+        <v>129995782</v>
       </c>
       <c r="B68" t="n">
-        <v>80104</v>
+        <v>79714</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532602</v>
+        <v>532409</v>
       </c>
       <c r="R68" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>129995798</v>
       </c>
       <c r="B71" t="n">
-        <v>98852</v>
+        <v>98854</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129995738</v>
+        <v>129995735</v>
       </c>
       <c r="B73" t="n">
-        <v>80229</v>
+        <v>91662</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532209</v>
+        <v>532609</v>
       </c>
       <c r="R73" t="n">
-        <v>7160509</v>
+        <v>7160604</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8688,7 +8688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995743</v>
+        <v>129995738</v>
       </c>
       <c r="B74" t="n">
         <v>80229</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532052</v>
+        <v>532209</v>
       </c>
       <c r="R74" t="n">
-        <v>7160499</v>
+        <v>7160509</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8789,32 +8789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995735</v>
+        <v>129995743</v>
       </c>
       <c r="B75" t="n">
-        <v>91660</v>
+        <v>80229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532609</v>
+        <v>532052</v>
       </c>
       <c r="R75" t="n">
-        <v>7160604</v>
+        <v>7160499</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9307,7 +9307,7 @@
         <v>129995764</v>
       </c>
       <c r="B80" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>129995746</v>
       </c>
       <c r="B81" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4850,7 +4850,7 @@
         <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>129995737</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129995772</v>
+        <v>129995741</v>
       </c>
       <c r="B38" t="n">
-        <v>91641</v>
+        <v>91748</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5061,23 +5061,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5085,13 +5081,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532563</v>
+        <v>532146</v>
       </c>
       <c r="R38" t="n">
-        <v>7160749</v>
+        <v>7160573</v>
       </c>
       <c r="S38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5151,10 +5147,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995741</v>
+        <v>129995760</v>
       </c>
       <c r="B39" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5162,33 +5158,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532146</v>
+        <v>532511</v>
       </c>
       <c r="R39" t="n">
-        <v>7160573</v>
+        <v>7160701</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995760</v>
+        <v>129995772</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,39 +5264,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532511</v>
+        <v>532563</v>
       </c>
       <c r="R40" t="n">
-        <v>7160701</v>
+        <v>7160749</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5357,7 +5357,7 @@
         <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         <v>129995776</v>
       </c>
       <c r="B43" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995763</v>
+        <v>129995744</v>
       </c>
       <c r="B44" t="n">
-        <v>80235</v>
+        <v>80314</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532539</v>
+        <v>532040</v>
       </c>
       <c r="R44" t="n">
-        <v>7160707</v>
+        <v>7160538</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>129995766</v>
       </c>
       <c r="B45" t="n">
-        <v>80236</v>
+        <v>80321</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995780</v>
+        <v>129995763</v>
       </c>
       <c r="B46" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532432</v>
+        <v>532539</v>
       </c>
       <c r="R46" t="n">
-        <v>7160802</v>
+        <v>7160707</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         <v>129995770</v>
       </c>
       <c r="B47" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6066,30 +6066,34 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995739</v>
+        <v>129995780</v>
       </c>
       <c r="B48" t="n">
-        <v>91661</v>
+        <v>80320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6097,10 +6101,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532158</v>
+        <v>532432</v>
       </c>
       <c r="R48" t="n">
-        <v>7160507</v>
+        <v>7160802</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6163,34 +6167,30 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995744</v>
+        <v>129995739</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>91748</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532040</v>
+        <v>532158</v>
       </c>
       <c r="R49" t="n">
-        <v>7160538</v>
+        <v>7160507</v>
       </c>
       <c r="S49" t="n">
         <v>2</v>
@@ -6264,34 +6264,30 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995757</v>
+        <v>129995767</v>
       </c>
       <c r="B50" t="n">
-        <v>80236</v>
+        <v>91748</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6299,13 +6295,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532504</v>
+        <v>532608</v>
       </c>
       <c r="R50" t="n">
-        <v>7160709</v>
+        <v>7160642</v>
       </c>
       <c r="S50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6368,7 +6364,7 @@
         <v>129995750</v>
       </c>
       <c r="B51" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6465,7 +6461,7 @@
         <v>129995748</v>
       </c>
       <c r="B52" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6562,7 +6558,7 @@
         <v>129995747</v>
       </c>
       <c r="B53" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6656,30 +6652,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995767</v>
+        <v>129995757</v>
       </c>
       <c r="B54" t="n">
-        <v>91661</v>
+        <v>80321</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532608</v>
+        <v>532504</v>
       </c>
       <c r="R54" t="n">
-        <v>7160642</v>
+        <v>7160709</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,32 +6753,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995759</v>
+        <v>129995769</v>
       </c>
       <c r="B55" t="n">
-        <v>80201</v>
+        <v>80320</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532498</v>
+        <v>532626</v>
       </c>
       <c r="R55" t="n">
-        <v>7160682</v>
+        <v>7160718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995769</v>
+        <v>129995762</v>
       </c>
       <c r="B56" t="n">
-        <v>80235</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532626</v>
+        <v>532540</v>
       </c>
       <c r="R56" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,10 +6955,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995771</v>
+        <v>129995755</v>
       </c>
       <c r="B57" t="n">
-        <v>91661</v>
+        <v>78937</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6966,19 +6966,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6986,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532562</v>
+        <v>532399</v>
       </c>
       <c r="R57" t="n">
-        <v>7160754</v>
+        <v>7160737</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7052,10 +7056,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995755</v>
+        <v>129995745</v>
       </c>
       <c r="B58" t="n">
-        <v>78852</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7063,37 +7067,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532399</v>
+        <v>532176</v>
       </c>
       <c r="R58" t="n">
-        <v>7160737</v>
+        <v>7160588</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7156,7 +7165,7 @@
         <v>129995753</v>
       </c>
       <c r="B59" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7254,32 +7263,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995762</v>
+        <v>129995759</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>80286</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7289,13 +7298,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532540</v>
+        <v>532498</v>
       </c>
       <c r="R60" t="n">
-        <v>7160698</v>
+        <v>7160682</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7355,10 +7364,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995745</v>
+        <v>129995771</v>
       </c>
       <c r="B61" t="n">
-        <v>57741</v>
+        <v>91748</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7366,42 +7375,33 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532176</v>
+        <v>532562</v>
       </c>
       <c r="R61" t="n">
-        <v>7160588</v>
+        <v>7160754</v>
       </c>
       <c r="S61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>129995756</v>
       </c>
       <c r="B62" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7562,48 +7562,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995779</v>
+        <v>129995777</v>
       </c>
       <c r="B63" t="n">
-        <v>80104</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532445</v>
+        <v>532500</v>
       </c>
       <c r="R63" t="n">
-        <v>7160791</v>
+        <v>7160787</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7666,7 +7671,7 @@
         <v>129995775</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7764,50 +7769,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995777</v>
+        <v>129995774</v>
       </c>
       <c r="B65" t="n">
-        <v>57741</v>
+        <v>80320</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532500</v>
+        <v>532519</v>
       </c>
       <c r="R65" t="n">
-        <v>7160787</v>
+        <v>7160765</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995774</v>
+        <v>129995779</v>
       </c>
       <c r="B66" t="n">
-        <v>80235</v>
+        <v>80189</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7905,13 +7905,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532519</v>
+        <v>532445</v>
       </c>
       <c r="R66" t="n">
-        <v>7160765</v>
+        <v>7160791</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7971,32 +7971,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995768</v>
+        <v>129995782</v>
       </c>
       <c r="B67" t="n">
-        <v>80104</v>
+        <v>79799</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532602</v>
+        <v>532409</v>
       </c>
       <c r="R67" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8072,32 +8072,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995782</v>
+        <v>129995798</v>
       </c>
       <c r="B68" t="n">
-        <v>79714</v>
+        <v>98941</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532409</v>
+        <v>532493</v>
       </c>
       <c r="R68" t="n">
-        <v>7160698</v>
+        <v>7160688</v>
       </c>
       <c r="S68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8173,32 +8173,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995758</v>
+        <v>129995768</v>
       </c>
       <c r="B69" t="n">
-        <v>80200</v>
+        <v>80189</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8208,10 +8208,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532501</v>
+        <v>532602</v>
       </c>
       <c r="R69" t="n">
-        <v>7160693</v>
+        <v>7160718</v>
       </c>
       <c r="S69" t="n">
         <v>2</v>
@@ -8277,7 +8277,7 @@
         <v>129995773</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8380,32 +8380,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129995798</v>
+        <v>129995758</v>
       </c>
       <c r="B71" t="n">
-        <v>98854</v>
+        <v>80285</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8415,13 +8415,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532493</v>
+        <v>532501</v>
       </c>
       <c r="R71" t="n">
-        <v>7160688</v>
+        <v>7160693</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8445,12 +8445,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8484,7 +8484,7 @@
         <v>129995751</v>
       </c>
       <c r="B72" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>129995735</v>
       </c>
       <c r="B73" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8688,10 +8688,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995738</v>
+        <v>129995743</v>
       </c>
       <c r="B74" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532209</v>
+        <v>532052</v>
       </c>
       <c r="R74" t="n">
-        <v>7160509</v>
+        <v>7160499</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8789,10 +8789,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995743</v>
+        <v>129995738</v>
       </c>
       <c r="B75" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532052</v>
+        <v>532209</v>
       </c>
       <c r="R75" t="n">
-        <v>7160499</v>
+        <v>7160509</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8890,10 +8890,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995742</v>
+        <v>129995778</v>
       </c>
       <c r="B76" t="n">
-        <v>80236</v>
+        <v>80314</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8901,21 +8901,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8925,10 +8925,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532090</v>
+        <v>532480</v>
       </c>
       <c r="R76" t="n">
-        <v>7160513</v>
+        <v>7160773</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
@@ -8991,45 +8991,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995778</v>
+        <v>129995749</v>
       </c>
       <c r="B77" t="n">
-        <v>80229</v>
+        <v>57826</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532480</v>
+        <v>532259</v>
       </c>
       <c r="R77" t="n">
-        <v>7160773</v>
+        <v>7160727</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9095,7 +9100,7 @@
         <v>129995740</v>
       </c>
       <c r="B78" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9198,50 +9203,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995749</v>
+        <v>129995742</v>
       </c>
       <c r="B79" t="n">
-        <v>57741</v>
+        <v>80321</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532259</v>
+        <v>532090</v>
       </c>
       <c r="R79" t="n">
-        <v>7160727</v>
+        <v>7160513</v>
       </c>
       <c r="S79" t="n">
         <v>2</v>
@@ -9307,7 +9307,7 @@
         <v>129995764</v>
       </c>
       <c r="B80" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>129995746</v>
       </c>
       <c r="B81" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>129995754</v>
       </c>
       <c r="B82" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>129995783</v>
       </c>
       <c r="B83" t="n">
-        <v>80160</v>
+        <v>80245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4847,10 +4847,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129995736</v>
+        <v>129995737</v>
       </c>
       <c r="B36" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4858,33 +4858,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532620</v>
+        <v>532200</v>
       </c>
       <c r="R36" t="n">
         <v>7160691</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4944,10 +4953,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129995737</v>
+        <v>129995736</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4955,42 +4964,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532200</v>
+        <v>532620</v>
       </c>
       <c r="R37" t="n">
         <v>7160691</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R41" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B42" t="n">
-        <v>80189</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R42" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995750</v>
+        <v>129995747</v>
       </c>
       <c r="B51" t="n">
         <v>91748</v>
@@ -6392,10 +6392,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532257</v>
+        <v>532181</v>
       </c>
       <c r="R51" t="n">
-        <v>7160770</v>
+        <v>7160703</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
@@ -6458,30 +6458,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995748</v>
+        <v>129995757</v>
       </c>
       <c r="B52" t="n">
-        <v>91748</v>
+        <v>80321</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6489,13 +6493,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532226</v>
+        <v>532504</v>
       </c>
       <c r="R52" t="n">
-        <v>7160724</v>
+        <v>7160709</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6555,7 +6559,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995747</v>
+        <v>129995750</v>
       </c>
       <c r="B53" t="n">
         <v>91748</v>
@@ -6586,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532181</v>
+        <v>532257</v>
       </c>
       <c r="R53" t="n">
-        <v>7160703</v>
+        <v>7160770</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6652,34 +6656,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995757</v>
+        <v>129995748</v>
       </c>
       <c r="B54" t="n">
-        <v>80321</v>
+        <v>91748</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532504</v>
+        <v>532226</v>
       </c>
       <c r="R54" t="n">
-        <v>7160709</v>
+        <v>7160724</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,32 +6753,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995769</v>
+        <v>129995755</v>
       </c>
       <c r="B55" t="n">
-        <v>80320</v>
+        <v>78937</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532626</v>
+        <v>532399</v>
       </c>
       <c r="R55" t="n">
-        <v>7160718</v>
+        <v>7160737</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6854,48 +6854,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995762</v>
+        <v>129995745</v>
       </c>
       <c r="B56" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532540</v>
+        <v>532176</v>
       </c>
       <c r="R56" t="n">
-        <v>7160698</v>
+        <v>7160588</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,32 +6960,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995755</v>
+        <v>129995753</v>
       </c>
       <c r="B57" t="n">
-        <v>78937</v>
+        <v>80314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6990,13 +6995,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532399</v>
+        <v>532432</v>
       </c>
       <c r="R57" t="n">
-        <v>7160737</v>
+        <v>7160788</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7056,53 +7061,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995745</v>
+        <v>129995769</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532176</v>
+        <v>532626</v>
       </c>
       <c r="R58" t="n">
-        <v>7160588</v>
+        <v>7160718</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995753</v>
+        <v>129995762</v>
       </c>
       <c r="B59" t="n">
         <v>80314</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532432</v>
+        <v>532540</v>
       </c>
       <c r="R59" t="n">
-        <v>7160788</v>
+        <v>7160698</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7971,32 +7971,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995782</v>
+        <v>129995798</v>
       </c>
       <c r="B67" t="n">
-        <v>79799</v>
+        <v>98941</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532409</v>
+        <v>532493</v>
       </c>
       <c r="R67" t="n">
-        <v>7160698</v>
+        <v>7160688</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995798</v>
+        <v>129995768</v>
       </c>
       <c r="B68" t="n">
-        <v>98941</v>
+        <v>80189</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532493</v>
+        <v>532602</v>
       </c>
       <c r="R68" t="n">
-        <v>7160688</v>
+        <v>7160718</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8173,32 +8173,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995768</v>
+        <v>129995782</v>
       </c>
       <c r="B69" t="n">
-        <v>80189</v>
+        <v>79799</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8208,13 +8208,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532602</v>
+        <v>532409</v>
       </c>
       <c r="R69" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4847,10 +4847,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129995737</v>
+        <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4858,42 +4858,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532200</v>
+        <v>532620</v>
       </c>
       <c r="R36" t="n">
         <v>7160691</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4953,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129995736</v>
+        <v>129995737</v>
       </c>
       <c r="B37" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4964,33 +4955,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532620</v>
+        <v>532200</v>
       </c>
       <c r="R37" t="n">
         <v>7160691</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R41" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R42" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995770</v>
+        <v>129995739</v>
       </c>
       <c r="B47" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5971,42 +5971,33 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532587</v>
+        <v>532158</v>
       </c>
       <c r="R47" t="n">
-        <v>7160733</v>
+        <v>7160507</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6066,48 +6057,53 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995780</v>
+        <v>129995770</v>
       </c>
       <c r="B48" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532432</v>
+        <v>532587</v>
       </c>
       <c r="R48" t="n">
-        <v>7160802</v>
+        <v>7160733</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6167,30 +6163,34 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995739</v>
+        <v>129995780</v>
       </c>
       <c r="B49" t="n">
-        <v>91748</v>
+        <v>80320</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6198,10 +6198,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532158</v>
+        <v>532432</v>
       </c>
       <c r="R49" t="n">
-        <v>7160507</v>
+        <v>7160802</v>
       </c>
       <c r="S49" t="n">
         <v>2</v>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995747</v>
+        <v>129995750</v>
       </c>
       <c r="B51" t="n">
         <v>91748</v>
@@ -6392,10 +6392,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532181</v>
+        <v>532257</v>
       </c>
       <c r="R51" t="n">
-        <v>7160703</v>
+        <v>7160770</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
@@ -6458,34 +6458,30 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995757</v>
+        <v>129995748</v>
       </c>
       <c r="B52" t="n">
-        <v>80321</v>
+        <v>91748</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6493,13 +6489,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532504</v>
+        <v>532226</v>
       </c>
       <c r="R52" t="n">
-        <v>7160709</v>
+        <v>7160724</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6559,7 +6555,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995750</v>
+        <v>129995747</v>
       </c>
       <c r="B53" t="n">
         <v>91748</v>
@@ -6590,10 +6586,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532257</v>
+        <v>532181</v>
       </c>
       <c r="R53" t="n">
-        <v>7160770</v>
+        <v>7160703</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6656,30 +6652,34 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995748</v>
+        <v>129995757</v>
       </c>
       <c r="B54" t="n">
-        <v>91748</v>
+        <v>80321</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532226</v>
+        <v>532504</v>
       </c>
       <c r="R54" t="n">
-        <v>7160724</v>
+        <v>7160709</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,32 +6753,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995755</v>
+        <v>129995769</v>
       </c>
       <c r="B55" t="n">
-        <v>78937</v>
+        <v>80320</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532399</v>
+        <v>532626</v>
       </c>
       <c r="R55" t="n">
-        <v>7160737</v>
+        <v>7160718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6854,53 +6854,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995745</v>
+        <v>129995762</v>
       </c>
       <c r="B56" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532176</v>
+        <v>532540</v>
       </c>
       <c r="R56" t="n">
-        <v>7160588</v>
+        <v>7160698</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6960,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995753</v>
+        <v>129995755</v>
       </c>
       <c r="B57" t="n">
-        <v>80314</v>
+        <v>78937</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6995,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532432</v>
+        <v>532399</v>
       </c>
       <c r="R57" t="n">
-        <v>7160788</v>
+        <v>7160737</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7061,48 +7056,53 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995769</v>
+        <v>129995745</v>
       </c>
       <c r="B58" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532626</v>
+        <v>532176</v>
       </c>
       <c r="R58" t="n">
-        <v>7160718</v>
+        <v>7160588</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995762</v>
+        <v>129995753</v>
       </c>
       <c r="B59" t="n">
         <v>80314</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532540</v>
+        <v>532432</v>
       </c>
       <c r="R59" t="n">
-        <v>7160698</v>
+        <v>7160788</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7971,32 +7971,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995798</v>
+        <v>129995782</v>
       </c>
       <c r="B67" t="n">
-        <v>98941</v>
+        <v>79799</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8006,13 +8006,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532493</v>
+        <v>532409</v>
       </c>
       <c r="R67" t="n">
-        <v>7160688</v>
+        <v>7160698</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8072,10 +8072,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995768</v>
+        <v>129995798</v>
       </c>
       <c r="B68" t="n">
-        <v>80189</v>
+        <v>98941</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8083,21 +8083,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6456</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532602</v>
+        <v>532493</v>
       </c>
       <c r="R68" t="n">
-        <v>7160718</v>
+        <v>7160688</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8173,32 +8173,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995782</v>
+        <v>129995768</v>
       </c>
       <c r="B69" t="n">
-        <v>79799</v>
+        <v>80189</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8208,13 +8208,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532409</v>
+        <v>532602</v>
       </c>
       <c r="R69" t="n">
-        <v>7160698</v>
+        <v>7160718</v>
       </c>
       <c r="S69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129995735</v>
+        <v>129995738</v>
       </c>
       <c r="B73" t="n">
-        <v>91749</v>
+        <v>80314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532609</v>
+        <v>532209</v>
       </c>
       <c r="R73" t="n">
-        <v>7160604</v>
+        <v>7160509</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8688,32 +8688,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995743</v>
+        <v>129995735</v>
       </c>
       <c r="B74" t="n">
-        <v>80314</v>
+        <v>91749</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532052</v>
+        <v>532609</v>
       </c>
       <c r="R74" t="n">
-        <v>7160499</v>
+        <v>7160604</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8789,7 +8789,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995738</v>
+        <v>129995743</v>
       </c>
       <c r="B75" t="n">
         <v>80314</v>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532209</v>
+        <v>532052</v>
       </c>
       <c r="R75" t="n">
-        <v>7160509</v>
+        <v>7160499</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8890,45 +8890,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995778</v>
+        <v>129995749</v>
       </c>
       <c r="B76" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532480</v>
+        <v>532259</v>
       </c>
       <c r="R76" t="n">
-        <v>7160773</v>
+        <v>7160727</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
@@ -8991,50 +8996,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995749</v>
+        <v>129995778</v>
       </c>
       <c r="B77" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532259</v>
+        <v>532480</v>
       </c>
       <c r="R77" t="n">
-        <v>7160727</v>
+        <v>7160773</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -5147,10 +5147,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995760</v>
+        <v>129995772</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5158,39 +5158,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532511</v>
+        <v>532563</v>
       </c>
       <c r="R39" t="n">
-        <v>7160701</v>
+        <v>7160749</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5253,10 +5248,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995772</v>
+        <v>129995760</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5264,34 +5259,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532563</v>
+        <v>532511</v>
       </c>
       <c r="R40" t="n">
-        <v>7160749</v>
+        <v>7160701</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B41" t="n">
-        <v>79180</v>
+        <v>80189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R41" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B42" t="n">
-        <v>80189</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R42" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995744</v>
+        <v>129995763</v>
       </c>
       <c r="B44" t="n">
-        <v>80314</v>
+        <v>80320</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5668,21 +5668,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5692,13 +5692,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532040</v>
+        <v>532539</v>
       </c>
       <c r="R44" t="n">
-        <v>7160538</v>
+        <v>7160707</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995763</v>
+        <v>129995780</v>
       </c>
       <c r="B46" t="n">
         <v>80320</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532539</v>
+        <v>532432</v>
       </c>
       <c r="R46" t="n">
-        <v>7160707</v>
+        <v>7160802</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6057,53 +6057,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995770</v>
+        <v>129995744</v>
       </c>
       <c r="B48" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532587</v>
+        <v>532040</v>
       </c>
       <c r="R48" t="n">
-        <v>7160733</v>
+        <v>7160538</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6163,48 +6158,53 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995780</v>
+        <v>129995770</v>
       </c>
       <c r="B49" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532432</v>
+        <v>532587</v>
       </c>
       <c r="R49" t="n">
-        <v>7160802</v>
+        <v>7160733</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995767</v>
+        <v>129995750</v>
       </c>
       <c r="B50" t="n">
         <v>91748</v>
@@ -6295,10 +6295,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532608</v>
+        <v>532257</v>
       </c>
       <c r="R50" t="n">
-        <v>7160642</v>
+        <v>7160770</v>
       </c>
       <c r="S50" t="n">
         <v>2</v>
@@ -6361,7 +6361,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995750</v>
+        <v>129995748</v>
       </c>
       <c r="B51" t="n">
         <v>91748</v>
@@ -6392,13 +6392,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532257</v>
+        <v>532226</v>
       </c>
       <c r="R51" t="n">
-        <v>7160770</v>
+        <v>7160724</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995748</v>
+        <v>129995747</v>
       </c>
       <c r="B52" t="n">
         <v>91748</v>
@@ -6489,13 +6489,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532226</v>
+        <v>532181</v>
       </c>
       <c r="R52" t="n">
-        <v>7160724</v>
+        <v>7160703</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995747</v>
+        <v>129995767</v>
       </c>
       <c r="B53" t="n">
         <v>91748</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532181</v>
+        <v>532608</v>
       </c>
       <c r="R53" t="n">
-        <v>7160703</v>
+        <v>7160642</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6753,48 +6753,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995769</v>
+        <v>129995745</v>
       </c>
       <c r="B55" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532626</v>
+        <v>532176</v>
       </c>
       <c r="R55" t="n">
-        <v>7160718</v>
+        <v>7160588</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6854,32 +6859,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995762</v>
+        <v>129995759</v>
       </c>
       <c r="B56" t="n">
-        <v>80314</v>
+        <v>80286</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,13 +6894,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532540</v>
+        <v>532498</v>
       </c>
       <c r="R56" t="n">
-        <v>7160698</v>
+        <v>7160682</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7056,53 +7061,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995745</v>
+        <v>129995769</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532176</v>
+        <v>532626</v>
       </c>
       <c r="R58" t="n">
-        <v>7160588</v>
+        <v>7160718</v>
       </c>
       <c r="S58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7263,32 +7263,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995759</v>
+        <v>129995762</v>
       </c>
       <c r="B60" t="n">
-        <v>80286</v>
+        <v>80314</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7298,13 +7298,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532498</v>
+        <v>532540</v>
       </c>
       <c r="R60" t="n">
-        <v>7160682</v>
+        <v>7160698</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7668,10 +7668,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995775</v>
+        <v>129995779</v>
       </c>
       <c r="B64" t="n">
-        <v>80314</v>
+        <v>80189</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7679,21 +7679,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7703,13 +7703,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532521</v>
+        <v>532445</v>
       </c>
       <c r="R64" t="n">
-        <v>7160766</v>
+        <v>7160791</v>
       </c>
       <c r="S64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7870,10 +7870,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129995779</v>
+        <v>129995775</v>
       </c>
       <c r="B66" t="n">
-        <v>80189</v>
+        <v>80314</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7881,21 +7881,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7905,13 +7905,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>532445</v>
+        <v>532521</v>
       </c>
       <c r="R66" t="n">
-        <v>7160791</v>
+        <v>7160766</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995782</v>
+        <v>129995773</v>
       </c>
       <c r="B67" t="n">
-        <v>79799</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7982,37 +7982,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532409</v>
+        <v>532558</v>
       </c>
       <c r="R67" t="n">
-        <v>7160698</v>
+        <v>7160752</v>
       </c>
       <c r="S67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8274,10 +8279,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995773</v>
+        <v>129995782</v>
       </c>
       <c r="B70" t="n">
-        <v>57826</v>
+        <v>79799</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8285,42 +8290,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532558</v>
+        <v>532409</v>
       </c>
       <c r="R70" t="n">
-        <v>7160752</v>
+        <v>7160698</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8688,32 +8688,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995735</v>
+        <v>129995743</v>
       </c>
       <c r="B74" t="n">
-        <v>91749</v>
+        <v>80314</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532609</v>
+        <v>532052</v>
       </c>
       <c r="R74" t="n">
-        <v>7160604</v>
+        <v>7160499</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8789,32 +8789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995743</v>
+        <v>129995735</v>
       </c>
       <c r="B75" t="n">
-        <v>80314</v>
+        <v>91749</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532052</v>
+        <v>532609</v>
       </c>
       <c r="R75" t="n">
-        <v>7160499</v>
+        <v>7160604</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8890,7 +8890,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995749</v>
+        <v>129995740</v>
       </c>
       <c r="B76" t="n">
         <v>57826</v>
@@ -8921,7 +8921,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8930,13 +8930,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532259</v>
+        <v>532123</v>
       </c>
       <c r="R76" t="n">
-        <v>7160727</v>
+        <v>7160541</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8996,45 +8996,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995778</v>
+        <v>129995749</v>
       </c>
       <c r="B77" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532480</v>
+        <v>532259</v>
       </c>
       <c r="R77" t="n">
-        <v>7160773</v>
+        <v>7160727</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9097,53 +9102,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B78" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R78" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4847,10 +4847,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129995736</v>
+        <v>129995737</v>
       </c>
       <c r="B36" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4858,33 +4858,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532620</v>
+        <v>532200</v>
       </c>
       <c r="R36" t="n">
         <v>7160691</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4944,10 +4953,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129995737</v>
+        <v>129995736</v>
       </c>
       <c r="B37" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4955,42 +4964,33 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532200</v>
+        <v>532620</v>
       </c>
       <c r="R37" t="n">
         <v>7160691</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995772</v>
+        <v>129995760</v>
       </c>
       <c r="B39" t="n">
-        <v>91728</v>
+        <v>57826</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5158,34 +5158,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532563</v>
+        <v>532511</v>
       </c>
       <c r="R39" t="n">
-        <v>7160749</v>
+        <v>7160701</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995760</v>
+        <v>129995772</v>
       </c>
       <c r="B40" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5259,39 +5264,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532511</v>
+        <v>532563</v>
       </c>
       <c r="R40" t="n">
-        <v>7160701</v>
+        <v>7160749</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -5354,32 +5354,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129995752</v>
+        <v>129995781</v>
       </c>
       <c r="B41" t="n">
-        <v>80189</v>
+        <v>79180</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5389,13 +5389,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>532432</v>
+        <v>532429</v>
       </c>
       <c r="R41" t="n">
-        <v>7160788</v>
+        <v>7160722</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5455,32 +5455,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129995781</v>
+        <v>129995752</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>80189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5490,13 +5490,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>532429</v>
+        <v>532432</v>
       </c>
       <c r="R42" t="n">
-        <v>7160722</v>
+        <v>7160788</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5657,34 +5657,30 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129995763</v>
+        <v>129995739</v>
       </c>
       <c r="B44" t="n">
-        <v>80320</v>
+        <v>91748</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5692,13 +5688,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>532539</v>
+        <v>532158</v>
       </c>
       <c r="R44" t="n">
-        <v>7160707</v>
+        <v>7160507</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5758,10 +5754,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995766</v>
+        <v>129995763</v>
       </c>
       <c r="B45" t="n">
-        <v>80321</v>
+        <v>80320</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5769,21 +5765,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5793,10 +5789,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532620</v>
+        <v>532539</v>
       </c>
       <c r="R45" t="n">
-        <v>7160493</v>
+        <v>7160707</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5859,10 +5855,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995780</v>
+        <v>129995766</v>
       </c>
       <c r="B46" t="n">
-        <v>80320</v>
+        <v>80321</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5870,21 +5866,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5894,13 +5890,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532432</v>
+        <v>532620</v>
       </c>
       <c r="R46" t="n">
-        <v>7160802</v>
+        <v>7160493</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5960,30 +5956,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995739</v>
+        <v>129995780</v>
       </c>
       <c r="B47" t="n">
-        <v>91748</v>
+        <v>80320</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532158</v>
+        <v>532432</v>
       </c>
       <c r="R47" t="n">
-        <v>7160507</v>
+        <v>7160802</v>
       </c>
       <c r="S47" t="n">
         <v>2</v>
@@ -6753,10 +6753,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995745</v>
+        <v>129995759</v>
       </c>
       <c r="B55" t="n">
-        <v>57826</v>
+        <v>80286</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6764,42 +6764,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532176</v>
+        <v>532498</v>
       </c>
       <c r="R55" t="n">
-        <v>7160588</v>
+        <v>7160682</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6859,32 +6854,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995759</v>
+        <v>129995769</v>
       </c>
       <c r="B56" t="n">
-        <v>80286</v>
+        <v>80320</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6894,10 +6889,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532498</v>
+        <v>532626</v>
       </c>
       <c r="R56" t="n">
-        <v>7160682</v>
+        <v>7160718</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6960,32 +6955,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995755</v>
+        <v>129995753</v>
       </c>
       <c r="B57" t="n">
-        <v>78937</v>
+        <v>80314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6995,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532399</v>
+        <v>532432</v>
       </c>
       <c r="R57" t="n">
-        <v>7160737</v>
+        <v>7160788</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7061,10 +7056,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995769</v>
+        <v>129995762</v>
       </c>
       <c r="B58" t="n">
-        <v>80320</v>
+        <v>80314</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7072,21 +7067,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7096,13 +7091,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532626</v>
+        <v>532540</v>
       </c>
       <c r="R58" t="n">
-        <v>7160718</v>
+        <v>7160698</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7162,32 +7157,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995753</v>
+        <v>129995755</v>
       </c>
       <c r="B59" t="n">
-        <v>80314</v>
+        <v>78937</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7197,13 +7192,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532432</v>
+        <v>532399</v>
       </c>
       <c r="R59" t="n">
-        <v>7160788</v>
+        <v>7160737</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7263,48 +7258,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129995762</v>
+        <v>129995745</v>
       </c>
       <c r="B60" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>532540</v>
+        <v>532176</v>
       </c>
       <c r="R60" t="n">
-        <v>7160698</v>
+        <v>7160588</v>
       </c>
       <c r="S60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7562,53 +7562,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995777</v>
+        <v>129995779</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>80189</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532500</v>
+        <v>532445</v>
       </c>
       <c r="R63" t="n">
-        <v>7160787</v>
+        <v>7160791</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7668,48 +7663,53 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995779</v>
+        <v>129995777</v>
       </c>
       <c r="B64" t="n">
-        <v>80189</v>
+        <v>57826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532445</v>
+        <v>532500</v>
       </c>
       <c r="R64" t="n">
-        <v>7160791</v>
+        <v>7160787</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129995738</v>
+        <v>129995735</v>
       </c>
       <c r="B73" t="n">
-        <v>80314</v>
+        <v>91749</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532209</v>
+        <v>532609</v>
       </c>
       <c r="R73" t="n">
-        <v>7160509</v>
+        <v>7160604</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8688,7 +8688,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129995743</v>
+        <v>129995738</v>
       </c>
       <c r="B74" t="n">
         <v>80314</v>
@@ -8723,10 +8723,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>532052</v>
+        <v>532209</v>
       </c>
       <c r="R74" t="n">
-        <v>7160499</v>
+        <v>7160509</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
@@ -8789,32 +8789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995735</v>
+        <v>129995743</v>
       </c>
       <c r="B75" t="n">
-        <v>91749</v>
+        <v>80314</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532609</v>
+        <v>532052</v>
       </c>
       <c r="R75" t="n">
-        <v>7160604</v>
+        <v>7160499</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8890,53 +8890,48 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B76" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R76" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8996,50 +8991,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995749</v>
+        <v>129995742</v>
       </c>
       <c r="B77" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532259</v>
+        <v>532090</v>
       </c>
       <c r="R77" t="n">
-        <v>7160727</v>
+        <v>7160513</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9102,45 +9092,50 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995778</v>
+        <v>129995749</v>
       </c>
       <c r="B78" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532480</v>
+        <v>532259</v>
       </c>
       <c r="R78" t="n">
-        <v>7160773</v>
+        <v>7160727</v>
       </c>
       <c r="S78" t="n">
         <v>2</v>
@@ -9203,48 +9198,53 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995742</v>
+        <v>129995740</v>
       </c>
       <c r="B79" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532090</v>
+        <v>532123</v>
       </c>
       <c r="R79" t="n">
-        <v>7160513</v>
+        <v>7160541</v>
       </c>
       <c r="S79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>

--- a/artfynd/A 12366-2025 artfynd.xlsx
+++ b/artfynd/A 12366-2025 artfynd.xlsx
@@ -4847,10 +4847,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129995737</v>
+        <v>129995736</v>
       </c>
       <c r="B36" t="n">
-        <v>57826</v>
+        <v>91748</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4858,42 +4858,33 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>532200</v>
+        <v>532620</v>
       </c>
       <c r="R36" t="n">
         <v>7160691</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4953,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129995736</v>
+        <v>129995737</v>
       </c>
       <c r="B37" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4964,33 +4955,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>532620</v>
+        <v>532200</v>
       </c>
       <c r="R37" t="n">
         <v>7160691</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129995741</v>
+        <v>129995760</v>
       </c>
       <c r="B38" t="n">
-        <v>91748</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5061,33 +5061,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>532146</v>
+        <v>532511</v>
       </c>
       <c r="R38" t="n">
-        <v>7160573</v>
+        <v>7160701</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5147,10 +5156,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129995760</v>
+        <v>129995772</v>
       </c>
       <c r="B39" t="n">
-        <v>57826</v>
+        <v>91728</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5158,39 +5167,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>532511</v>
+        <v>532563</v>
       </c>
       <c r="R39" t="n">
-        <v>7160701</v>
+        <v>7160749</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -5253,10 +5257,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129995772</v>
+        <v>129995741</v>
       </c>
       <c r="B40" t="n">
-        <v>91728</v>
+        <v>91748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5264,23 +5268,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5288,13 +5288,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>532563</v>
+        <v>532146</v>
       </c>
       <c r="R40" t="n">
-        <v>7160749</v>
+        <v>7160573</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5754,45 +5754,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129995763</v>
+        <v>129995770</v>
       </c>
       <c r="B45" t="n">
-        <v>80320</v>
+        <v>57826</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>532539</v>
+        <v>532587</v>
       </c>
       <c r="R45" t="n">
-        <v>7160707</v>
+        <v>7160733</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5855,10 +5860,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129995766</v>
+        <v>129995763</v>
       </c>
       <c r="B46" t="n">
-        <v>80321</v>
+        <v>80320</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5866,21 +5871,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5890,10 +5895,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>532620</v>
+        <v>532539</v>
       </c>
       <c r="R46" t="n">
-        <v>7160493</v>
+        <v>7160707</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5956,10 +5961,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129995780</v>
+        <v>129995744</v>
       </c>
       <c r="B47" t="n">
-        <v>80320</v>
+        <v>80314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5967,21 +5972,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5991,10 +5996,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>532432</v>
+        <v>532040</v>
       </c>
       <c r="R47" t="n">
-        <v>7160802</v>
+        <v>7160538</v>
       </c>
       <c r="S47" t="n">
         <v>2</v>
@@ -6057,10 +6062,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129995744</v>
+        <v>129995780</v>
       </c>
       <c r="B48" t="n">
-        <v>80314</v>
+        <v>80320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6068,21 +6073,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6092,10 +6097,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>532040</v>
+        <v>532432</v>
       </c>
       <c r="R48" t="n">
-        <v>7160538</v>
+        <v>7160802</v>
       </c>
       <c r="S48" t="n">
         <v>2</v>
@@ -6158,50 +6163,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129995770</v>
+        <v>129995766</v>
       </c>
       <c r="B49" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>532587</v>
+        <v>532620</v>
       </c>
       <c r="R49" t="n">
-        <v>7160733</v>
+        <v>7160493</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6264,30 +6264,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129995750</v>
+        <v>129995757</v>
       </c>
       <c r="B50" t="n">
-        <v>91748</v>
+        <v>80321</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6295,13 +6299,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>532257</v>
+        <v>532504</v>
       </c>
       <c r="R50" t="n">
-        <v>7160770</v>
+        <v>7160709</v>
       </c>
       <c r="S50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,7 +6365,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129995748</v>
+        <v>129995750</v>
       </c>
       <c r="B51" t="n">
         <v>91748</v>
@@ -6392,13 +6396,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>532226</v>
+        <v>532257</v>
       </c>
       <c r="R51" t="n">
-        <v>7160724</v>
+        <v>7160770</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6458,7 +6462,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129995747</v>
+        <v>129995748</v>
       </c>
       <c r="B52" t="n">
         <v>91748</v>
@@ -6489,13 +6493,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>532181</v>
+        <v>532226</v>
       </c>
       <c r="R52" t="n">
-        <v>7160703</v>
+        <v>7160724</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6555,7 +6559,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129995767</v>
+        <v>129995747</v>
       </c>
       <c r="B53" t="n">
         <v>91748</v>
@@ -6586,10 +6590,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>532608</v>
+        <v>532181</v>
       </c>
       <c r="R53" t="n">
-        <v>7160642</v>
+        <v>7160703</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6652,34 +6656,30 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129995757</v>
+        <v>129995767</v>
       </c>
       <c r="B54" t="n">
-        <v>80321</v>
+        <v>91748</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6687,13 +6687,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>532504</v>
+        <v>532608</v>
       </c>
       <c r="R54" t="n">
-        <v>7160709</v>
+        <v>7160642</v>
       </c>
       <c r="S54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6753,32 +6753,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129995759</v>
+        <v>129995769</v>
       </c>
       <c r="B55" t="n">
-        <v>80286</v>
+        <v>80320</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6788,10 +6788,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>532498</v>
+        <v>532626</v>
       </c>
       <c r="R55" t="n">
-        <v>7160682</v>
+        <v>7160718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6854,10 +6854,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129995769</v>
+        <v>129995753</v>
       </c>
       <c r="B56" t="n">
-        <v>80320</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6865,21 +6865,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>532626</v>
+        <v>532432</v>
       </c>
       <c r="R56" t="n">
-        <v>7160718</v>
+        <v>7160788</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129995753</v>
+        <v>129995762</v>
       </c>
       <c r="B57" t="n">
         <v>80314</v>
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>532432</v>
+        <v>532540</v>
       </c>
       <c r="R57" t="n">
-        <v>7160788</v>
+        <v>7160698</v>
       </c>
       <c r="S57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7056,32 +7056,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129995762</v>
+        <v>129995755</v>
       </c>
       <c r="B58" t="n">
-        <v>80314</v>
+        <v>78937</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>532540</v>
+        <v>532399</v>
       </c>
       <c r="R58" t="n">
-        <v>7160698</v>
+        <v>7160737</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129995755</v>
+        <v>129995771</v>
       </c>
       <c r="B59" t="n">
-        <v>78937</v>
+        <v>91748</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7168,23 +7168,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7192,13 +7188,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>532399</v>
+        <v>532562</v>
       </c>
       <c r="R59" t="n">
-        <v>7160737</v>
+        <v>7160754</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7364,10 +7360,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129995771</v>
+        <v>129995759</v>
       </c>
       <c r="B61" t="n">
-        <v>91748</v>
+        <v>80286</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7375,19 +7371,23 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7395,13 +7395,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>532562</v>
+        <v>532498</v>
       </c>
       <c r="R61" t="n">
-        <v>7160754</v>
+        <v>7160682</v>
       </c>
       <c r="S61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7562,48 +7562,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129995779</v>
+        <v>129995777</v>
       </c>
       <c r="B63" t="n">
-        <v>80189</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>532445</v>
+        <v>532500</v>
       </c>
       <c r="R63" t="n">
-        <v>7160791</v>
+        <v>7160787</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7663,50 +7668,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129995777</v>
+        <v>129995774</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>80320</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>532500</v>
+        <v>532519</v>
       </c>
       <c r="R64" t="n">
-        <v>7160787</v>
+        <v>7160765</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7769,10 +7769,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129995774</v>
+        <v>129995779</v>
       </c>
       <c r="B65" t="n">
-        <v>80320</v>
+        <v>80189</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7780,21 +7780,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7804,13 +7804,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>532519</v>
+        <v>532445</v>
       </c>
       <c r="R65" t="n">
-        <v>7160765</v>
+        <v>7160791</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7971,10 +7971,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129995773</v>
+        <v>129995782</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>79799</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7982,42 +7982,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>532558</v>
+        <v>532409</v>
       </c>
       <c r="R67" t="n">
-        <v>7160752</v>
+        <v>7160698</v>
       </c>
       <c r="S67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8077,10 +8072,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129995798</v>
+        <v>129995768</v>
       </c>
       <c r="B68" t="n">
-        <v>98941</v>
+        <v>80189</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8088,21 +8083,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>6456</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8112,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>532493</v>
+        <v>532602</v>
       </c>
       <c r="R68" t="n">
-        <v>7160688</v>
+        <v>7160718</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8142,12 +8137,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8167,7 +8162,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8178,32 +8173,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129995768</v>
+        <v>129995758</v>
       </c>
       <c r="B69" t="n">
-        <v>80189</v>
+        <v>80285</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8213,10 +8208,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>532602</v>
+        <v>532501</v>
       </c>
       <c r="R69" t="n">
-        <v>7160718</v>
+        <v>7160693</v>
       </c>
       <c r="S69" t="n">
         <v>2</v>
@@ -8279,32 +8274,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129995782</v>
+        <v>129995798</v>
       </c>
       <c r="B70" t="n">
-        <v>79799</v>
+        <v>98941</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8314,13 +8309,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>532409</v>
+        <v>532493</v>
       </c>
       <c r="R70" t="n">
-        <v>7160698</v>
+        <v>7160688</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8344,12 +8339,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8369,7 +8364,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Emma Munters</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8380,10 +8375,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129995758</v>
+        <v>129995773</v>
       </c>
       <c r="B71" t="n">
-        <v>80285</v>
+        <v>57826</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8391,34 +8386,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>532501</v>
+        <v>532558</v>
       </c>
       <c r="R71" t="n">
-        <v>7160693</v>
+        <v>7160752</v>
       </c>
       <c r="S71" t="n">
         <v>2</v>
@@ -8587,32 +8587,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129995735</v>
+        <v>129995743</v>
       </c>
       <c r="B73" t="n">
-        <v>91749</v>
+        <v>80314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>532609</v>
+        <v>532052</v>
       </c>
       <c r="R73" t="n">
-        <v>7160604</v>
+        <v>7160499</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -8652,12 +8652,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8789,32 +8789,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129995743</v>
+        <v>129995735</v>
       </c>
       <c r="B75" t="n">
-        <v>80314</v>
+        <v>91749</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8824,10 +8824,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>532052</v>
+        <v>532609</v>
       </c>
       <c r="R75" t="n">
-        <v>7160499</v>
+        <v>7160604</v>
       </c>
       <c r="S75" t="n">
         <v>2</v>
@@ -8854,12 +8854,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8890,48 +8890,53 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129995778</v>
+        <v>129995740</v>
       </c>
       <c r="B76" t="n">
-        <v>80314</v>
+        <v>57826</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>532480</v>
+        <v>532123</v>
       </c>
       <c r="R76" t="n">
-        <v>7160773</v>
+        <v>7160541</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8991,45 +8996,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129995742</v>
+        <v>129995749</v>
       </c>
       <c r="B77" t="n">
-        <v>80321</v>
+        <v>57826</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>532090</v>
+        <v>532259</v>
       </c>
       <c r="R77" t="n">
-        <v>7160513</v>
+        <v>7160727</v>
       </c>
       <c r="S77" t="n">
         <v>2</v>
@@ -9092,50 +9102,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129995749</v>
+        <v>129995742</v>
       </c>
       <c r="B78" t="n">
-        <v>57826</v>
+        <v>80321</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>532259</v>
+        <v>532090</v>
       </c>
       <c r="R78" t="n">
-        <v>7160727</v>
+        <v>7160513</v>
       </c>
       <c r="S78" t="n">
         <v>2</v>
@@ -9198,53 +9203,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129995740</v>
+        <v>129995778</v>
       </c>
       <c r="B79" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Pissfisktjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>532123</v>
+        <v>532480</v>
       </c>
       <c r="R79" t="n">
-        <v>7160541</v>
+        <v>7160773</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
